--- a/artfynd/A 58107-2025 artfynd.xlsx
+++ b/artfynd/A 58107-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2541,6 +2541,4514 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129926723</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>65</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Fläckporing</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Anthoporia albobrunnea</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>444348</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6924034</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129926722</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92881</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>444366</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6924005</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129926699</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79671</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>444138</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6923625</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129926725</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79700</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>444315</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6923974</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129926727</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79671</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>444295</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6923949</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129926707</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78839</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>444272</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6923791</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129926738</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80221</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>444051</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6923830</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129926714</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91772</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>444331</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6923827</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129926731</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78839</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>444190</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6923908</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129926700</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78839</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>444139</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6923624</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129926726</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57896</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>444309</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6923959</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129926737</v>
+      </c>
+      <c r="B29" t="n">
+        <v>92919</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>444073</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6923833</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129926696</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80186</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>444018</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6923684</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129926729</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92881</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>444210</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6923955</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129926718</v>
+      </c>
+      <c r="B32" t="n">
+        <v>97667</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>444362</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6923872</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129926697</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>444080</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6923635</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129926712</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80221</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>444339</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6923809</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129926705</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80221</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>444117</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6923735</v>
+      </c>
+      <c r="S35" t="n">
+        <v>4</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129926698</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79671</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>444118</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6923621</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129926715</v>
+      </c>
+      <c r="B37" t="n">
+        <v>92241</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5454</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Hornvaxskinn</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Crustoderma corneum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>444350</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6923880</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129926734</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78747</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>353</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>444169</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6923886</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129926704</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80222</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>444124</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6923727</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129926710</v>
+      </c>
+      <c r="B40" t="n">
+        <v>92881</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>444283</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6923819</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129926721</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79671</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>444365</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6923915</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129926720</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91772</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>444360</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6923918</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129926706</v>
+      </c>
+      <c r="B43" t="n">
+        <v>90422</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>444279</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6923782</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129926724</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78839</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>444330</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6923984</v>
+      </c>
+      <c r="S44" t="n">
+        <v>4</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129926728</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91652</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>444229</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6923882</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129926702</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98790</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>444122</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6923680</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129926701</v>
+      </c>
+      <c r="B47" t="n">
+        <v>105856</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>444126</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6923694</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129926709</v>
+      </c>
+      <c r="B48" t="n">
+        <v>91522</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>444268</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6923829</v>
+      </c>
+      <c r="S48" t="n">
+        <v>3</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129926730</v>
+      </c>
+      <c r="B49" t="n">
+        <v>78484</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>444200</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6923914</v>
+      </c>
+      <c r="S49" t="n">
+        <v>3</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129926733</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79671</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>444163</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6923898</v>
+      </c>
+      <c r="S50" t="n">
+        <v>3</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129926713</v>
+      </c>
+      <c r="B51" t="n">
+        <v>91522</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>444347</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6923828</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Under grov, gammal nedfallen tallgren.</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129926736</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78838</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>444093</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6923866</v>
+      </c>
+      <c r="S52" t="n">
+        <v>4</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129926703</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98790</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>444124</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6923712</v>
+      </c>
+      <c r="S53" t="n">
+        <v>4</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129926717</v>
+      </c>
+      <c r="B54" t="n">
+        <v>91613</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>444352</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6923879</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129926735</v>
+      </c>
+      <c r="B55" t="n">
+        <v>91772</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>444143</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6923881</v>
+      </c>
+      <c r="S55" t="n">
+        <v>4</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129926716</v>
+      </c>
+      <c r="B56" t="n">
+        <v>91772</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>444351</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6923878</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129926708</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79671</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>444257</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6923818</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58107-2025 artfynd.xlsx
+++ b/artfynd/A 58107-2025 artfynd.xlsx
@@ -2543,32 +2543,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129926723</v>
+        <v>129926699</v>
       </c>
       <c r="B18" t="n">
-        <v>91872</v>
+        <v>79674</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>65</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444348</v>
+        <v>444138</v>
       </c>
       <c r="R18" t="n">
-        <v>6924034</v>
+        <v>6923625</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2657,7 +2657,7 @@
         <v>129926722</v>
       </c>
       <c r="B19" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2765,32 +2765,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129926699</v>
+        <v>129926723</v>
       </c>
       <c r="B20" t="n">
-        <v>79671</v>
+        <v>91875</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>65</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444138</v>
+        <v>444348</v>
       </c>
       <c r="R20" t="n">
-        <v>6923625</v>
+        <v>6924034</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2879,7 +2879,7 @@
         <v>129926725</v>
       </c>
       <c r="B21" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2987,32 +2987,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129926727</v>
+        <v>129926738</v>
       </c>
       <c r="B22" t="n">
-        <v>79671</v>
+        <v>80224</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3022,13 +3022,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444295</v>
+        <v>444051</v>
       </c>
       <c r="R22" t="n">
-        <v>6923949</v>
+        <v>6923830</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3098,10 +3098,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129926707</v>
+        <v>129926727</v>
       </c>
       <c r="B23" t="n">
-        <v>78839</v>
+        <v>79674</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3109,21 +3109,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3133,13 +3133,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444272</v>
+        <v>444295</v>
       </c>
       <c r="R23" t="n">
-        <v>6923791</v>
+        <v>6923949</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3209,32 +3209,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129926738</v>
+        <v>129926707</v>
       </c>
       <c r="B24" t="n">
-        <v>80221</v>
+        <v>78842</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3244,13 +3244,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444051</v>
+        <v>444272</v>
       </c>
       <c r="R24" t="n">
-        <v>6923830</v>
+        <v>6923791</v>
       </c>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3320,32 +3320,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129926714</v>
+        <v>129926731</v>
       </c>
       <c r="B25" t="n">
-        <v>91772</v>
+        <v>78842</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444331</v>
+        <v>444190</v>
       </c>
       <c r="R25" t="n">
-        <v>6923827</v>
+        <v>6923908</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3431,10 +3431,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129926731</v>
+        <v>129926700</v>
       </c>
       <c r="B26" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444190</v>
+        <v>444139</v>
       </c>
       <c r="R26" t="n">
-        <v>6923908</v>
+        <v>6923624</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3542,32 +3542,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129926700</v>
+        <v>129926714</v>
       </c>
       <c r="B27" t="n">
-        <v>78839</v>
+        <v>91775</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3577,10 +3577,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444139</v>
+        <v>444331</v>
       </c>
       <c r="R27" t="n">
-        <v>6923624</v>
+        <v>6923827</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3653,10 +3653,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129926726</v>
+        <v>129926737</v>
       </c>
       <c r="B28" t="n">
-        <v>57896</v>
+        <v>92922</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3664,37 +3664,46 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444309</v>
+        <v>444073</v>
       </c>
       <c r="R28" t="n">
-        <v>6923959</v>
+        <v>6923833</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3723,7 +3732,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3733,7 +3742,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3764,10 +3773,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129926737</v>
+        <v>129926726</v>
       </c>
       <c r="B29" t="n">
-        <v>92919</v>
+        <v>57895</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3775,46 +3784,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444073</v>
+        <v>444309</v>
       </c>
       <c r="R29" t="n">
-        <v>6923833</v>
+        <v>6923959</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3887,7 +3887,7 @@
         <v>129926696</v>
       </c>
       <c r="B30" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>129926729</v>
       </c>
       <c r="B31" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4115,10 +4115,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129926718</v>
+        <v>129926712</v>
       </c>
       <c r="B32" t="n">
-        <v>97667</v>
+        <v>80224</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4126,21 +4126,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221941</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444362</v>
+        <v>444339</v>
       </c>
       <c r="R32" t="n">
-        <v>6923872</v>
+        <v>6923809</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4226,10 +4226,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129926697</v>
+        <v>129926698</v>
       </c>
       <c r="B33" t="n">
-        <v>57736</v>
+        <v>79674</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4237,43 +4237,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444080</v>
+        <v>444118</v>
       </c>
       <c r="R33" t="n">
-        <v>6923635</v>
+        <v>6923621</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4305,7 +4296,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4315,7 +4306,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4346,45 +4337,54 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129926712</v>
+        <v>129926697</v>
       </c>
       <c r="B34" t="n">
-        <v>80221</v>
+        <v>57737</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444339</v>
+        <v>444080</v>
       </c>
       <c r="R34" t="n">
-        <v>6923809</v>
+        <v>6923635</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4460,7 +4460,7 @@
         <v>129926705</v>
       </c>
       <c r="B35" t="n">
-        <v>80221</v>
+        <v>80224</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4568,32 +4568,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129926698</v>
+        <v>129926718</v>
       </c>
       <c r="B36" t="n">
-        <v>79671</v>
+        <v>97671</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>221941</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444118</v>
+        <v>444362</v>
       </c>
       <c r="R36" t="n">
-        <v>6923621</v>
+        <v>6923872</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4682,7 +4682,7 @@
         <v>129926715</v>
       </c>
       <c r="B37" t="n">
-        <v>92241</v>
+        <v>92244</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>129926734</v>
       </c>
       <c r="B38" t="n">
-        <v>78747</v>
+        <v>78750</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4901,10 +4901,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129926704</v>
+        <v>129926710</v>
       </c>
       <c r="B39" t="n">
-        <v>80222</v>
+        <v>92884</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4912,34 +4912,43 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444124</v>
+        <v>444283</v>
       </c>
       <c r="R39" t="n">
-        <v>6923727</v>
+        <v>6923819</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4971,7 +4980,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4981,7 +4990,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5012,10 +5021,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129926710</v>
+        <v>129926704</v>
       </c>
       <c r="B40" t="n">
-        <v>92881</v>
+        <v>80225</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5023,43 +5032,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444283</v>
+        <v>444124</v>
       </c>
       <c r="R40" t="n">
-        <v>6923819</v>
+        <v>6923727</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5132,32 +5132,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129926721</v>
+        <v>129926720</v>
       </c>
       <c r="B41" t="n">
-        <v>79671</v>
+        <v>91775</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444365</v>
+        <v>444360</v>
       </c>
       <c r="R41" t="n">
-        <v>6923915</v>
+        <v>6923918</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5243,32 +5243,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129926720</v>
+        <v>129926721</v>
       </c>
       <c r="B42" t="n">
-        <v>91772</v>
+        <v>79674</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5278,10 +5278,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444360</v>
+        <v>444365</v>
       </c>
       <c r="R42" t="n">
-        <v>6923918</v>
+        <v>6923915</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5357,7 +5357,7 @@
         <v>129926706</v>
       </c>
       <c r="B43" t="n">
-        <v>90422</v>
+        <v>90425</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>129926724</v>
       </c>
       <c r="B44" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5585,10 +5585,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129926728</v>
+        <v>129926709</v>
       </c>
       <c r="B45" t="n">
-        <v>91652</v>
+        <v>91525</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5596,21 +5596,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2079</v>
+        <v>3242</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5620,13 +5620,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444229</v>
+        <v>444268</v>
       </c>
       <c r="R45" t="n">
-        <v>6923882</v>
+        <v>6923829</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5696,54 +5696,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129926702</v>
+        <v>129926701</v>
       </c>
       <c r="B46" t="n">
-        <v>98790</v>
+        <v>105860</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444122</v>
+        <v>444126</v>
       </c>
       <c r="R46" t="n">
-        <v>6923680</v>
+        <v>6923694</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5816,32 +5807,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129926701</v>
+        <v>129926728</v>
       </c>
       <c r="B47" t="n">
-        <v>105856</v>
+        <v>91655</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>2079</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5851,10 +5842,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444126</v>
+        <v>444229</v>
       </c>
       <c r="R47" t="n">
-        <v>6923694</v>
+        <v>6923882</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5886,7 +5877,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5896,7 +5887,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5927,48 +5918,57 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129926709</v>
+        <v>129926702</v>
       </c>
       <c r="B48" t="n">
-        <v>91522</v>
+        <v>98794</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3242</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444268</v>
+        <v>444122</v>
       </c>
       <c r="R48" t="n">
-        <v>6923829</v>
+        <v>6923680</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6041,7 +6041,7 @@
         <v>129926730</v>
       </c>
       <c r="B49" t="n">
-        <v>78484</v>
+        <v>78487</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>129926733</v>
       </c>
       <c r="B50" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>129926713</v>
       </c>
       <c r="B51" t="n">
-        <v>91522</v>
+        <v>91525</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6376,45 +6376,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129926736</v>
+        <v>129926703</v>
       </c>
       <c r="B52" t="n">
-        <v>78838</v>
+        <v>98794</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444093</v>
+        <v>444124</v>
       </c>
       <c r="R52" t="n">
-        <v>6923866</v>
+        <v>6923712</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6446,7 +6455,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6456,7 +6465,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6487,54 +6496,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129926703</v>
+        <v>129926736</v>
       </c>
       <c r="B53" t="n">
-        <v>98790</v>
+        <v>78841</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444124</v>
+        <v>444093</v>
       </c>
       <c r="R53" t="n">
-        <v>6923712</v>
+        <v>6923866</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6610,7 +6610,7 @@
         <v>129926717</v>
       </c>
       <c r="B54" t="n">
-        <v>91613</v>
+        <v>91616</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>129926735</v>
       </c>
       <c r="B55" t="n">
-        <v>91772</v>
+        <v>91775</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
         <v>129926716</v>
       </c>
       <c r="B56" t="n">
-        <v>91772</v>
+        <v>91775</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>129926708</v>
       </c>
       <c r="B57" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 58107-2025 artfynd.xlsx
+++ b/artfynd/A 58107-2025 artfynd.xlsx
@@ -2543,32 +2543,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129926699</v>
+        <v>129926722</v>
       </c>
       <c r="B18" t="n">
-        <v>79674</v>
+        <v>92884</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444138</v>
+        <v>444366</v>
       </c>
       <c r="R18" t="n">
-        <v>6923625</v>
+        <v>6924005</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2654,32 +2654,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129926722</v>
+        <v>129926725</v>
       </c>
       <c r="B19" t="n">
-        <v>92884</v>
+        <v>79703</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444366</v>
+        <v>444315</v>
       </c>
       <c r="R19" t="n">
-        <v>6924005</v>
+        <v>6923974</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2876,10 +2876,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129926725</v>
+        <v>129926699</v>
       </c>
       <c r="B21" t="n">
-        <v>79703</v>
+        <v>79674</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2887,21 +2887,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2911,10 +2911,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444315</v>
+        <v>444138</v>
       </c>
       <c r="R21" t="n">
-        <v>6923974</v>
+        <v>6923625</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3098,10 +3098,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129926727</v>
+        <v>129926707</v>
       </c>
       <c r="B23" t="n">
-        <v>79674</v>
+        <v>78842</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3109,21 +3109,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3133,13 +3133,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444295</v>
+        <v>444272</v>
       </c>
       <c r="R23" t="n">
-        <v>6923949</v>
+        <v>6923791</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3209,10 +3209,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129926707</v>
+        <v>129926727</v>
       </c>
       <c r="B24" t="n">
-        <v>78842</v>
+        <v>79674</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3220,21 +3220,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3244,13 +3244,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444272</v>
+        <v>444295</v>
       </c>
       <c r="R24" t="n">
-        <v>6923791</v>
+        <v>6923949</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3320,32 +3320,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129926731</v>
+        <v>129926714</v>
       </c>
       <c r="B25" t="n">
-        <v>78842</v>
+        <v>91775</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444190</v>
+        <v>444331</v>
       </c>
       <c r="R25" t="n">
-        <v>6923908</v>
+        <v>6923827</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3431,7 +3431,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129926700</v>
+        <v>129926731</v>
       </c>
       <c r="B26" t="n">
         <v>78842</v>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444139</v>
+        <v>444190</v>
       </c>
       <c r="R26" t="n">
-        <v>6923624</v>
+        <v>6923908</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3542,32 +3542,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129926714</v>
+        <v>129926700</v>
       </c>
       <c r="B27" t="n">
-        <v>91775</v>
+        <v>78842</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3577,10 +3577,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444331</v>
+        <v>444139</v>
       </c>
       <c r="R27" t="n">
-        <v>6923827</v>
+        <v>6923624</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3653,10 +3653,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129926737</v>
+        <v>129926726</v>
       </c>
       <c r="B28" t="n">
-        <v>92922</v>
+        <v>57895</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3664,46 +3664,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444073</v>
+        <v>444309</v>
       </c>
       <c r="R28" t="n">
-        <v>6923833</v>
+        <v>6923959</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3732,7 +3723,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3742,7 +3733,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3773,10 +3764,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129926726</v>
+        <v>129926737</v>
       </c>
       <c r="B29" t="n">
-        <v>57895</v>
+        <v>92922</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3784,37 +3775,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444309</v>
+        <v>444073</v>
       </c>
       <c r="R29" t="n">
-        <v>6923959</v>
+        <v>6923833</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4226,32 +4226,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129926698</v>
+        <v>129926705</v>
       </c>
       <c r="B33" t="n">
-        <v>79674</v>
+        <v>80224</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>6463</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4261,13 +4261,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444118</v>
+        <v>444117</v>
       </c>
       <c r="R33" t="n">
-        <v>6923621</v>
+        <v>6923735</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4337,54 +4337,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129926697</v>
+        <v>129926718</v>
       </c>
       <c r="B34" t="n">
-        <v>57737</v>
+        <v>97671</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444080</v>
+        <v>444362</v>
       </c>
       <c r="R34" t="n">
-        <v>6923635</v>
+        <v>6923872</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4416,7 +4407,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4426,7 +4417,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4457,32 +4448,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129926705</v>
+        <v>129926698</v>
       </c>
       <c r="B35" t="n">
-        <v>80224</v>
+        <v>79674</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6463</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4492,13 +4483,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444117</v>
+        <v>444118</v>
       </c>
       <c r="R35" t="n">
-        <v>6923735</v>
+        <v>6923621</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4527,7 +4518,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4537,7 +4528,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4568,45 +4559,54 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129926718</v>
+        <v>129926697</v>
       </c>
       <c r="B36" t="n">
-        <v>97671</v>
+        <v>57737</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444362</v>
+        <v>444080</v>
       </c>
       <c r="R36" t="n">
-        <v>6923872</v>
+        <v>6923635</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5132,32 +5132,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129926720</v>
+        <v>129926721</v>
       </c>
       <c r="B41" t="n">
-        <v>91775</v>
+        <v>79674</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444360</v>
+        <v>444365</v>
       </c>
       <c r="R41" t="n">
-        <v>6923918</v>
+        <v>6923915</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5243,32 +5243,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129926721</v>
+        <v>129926720</v>
       </c>
       <c r="B42" t="n">
-        <v>79674</v>
+        <v>91775</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5278,10 +5278,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444365</v>
+        <v>444360</v>
       </c>
       <c r="R42" t="n">
-        <v>6923915</v>
+        <v>6923918</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5585,10 +5585,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129926709</v>
+        <v>129926728</v>
       </c>
       <c r="B45" t="n">
-        <v>91525</v>
+        <v>91655</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5596,21 +5596,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3242</v>
+        <v>2079</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5620,13 +5620,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444268</v>
+        <v>444229</v>
       </c>
       <c r="R45" t="n">
-        <v>6923829</v>
+        <v>6923882</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5696,32 +5696,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129926701</v>
+        <v>129926709</v>
       </c>
       <c r="B46" t="n">
-        <v>105860</v>
+        <v>91525</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221144</v>
+        <v>3242</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5731,13 +5731,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444126</v>
+        <v>444268</v>
       </c>
       <c r="R46" t="n">
-        <v>6923694</v>
+        <v>6923829</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5807,45 +5807,54 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129926728</v>
+        <v>129926702</v>
       </c>
       <c r="B47" t="n">
-        <v>91655</v>
+        <v>98794</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444229</v>
+        <v>444122</v>
       </c>
       <c r="R47" t="n">
-        <v>6923882</v>
+        <v>6923680</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5877,7 +5886,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5887,7 +5896,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5918,54 +5927,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129926702</v>
+        <v>129926701</v>
       </c>
       <c r="B48" t="n">
-        <v>98794</v>
+        <v>105860</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444122</v>
+        <v>444126</v>
       </c>
       <c r="R48" t="n">
-        <v>6923680</v>
+        <v>6923694</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6376,54 +6376,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129926703</v>
+        <v>129926736</v>
       </c>
       <c r="B52" t="n">
-        <v>98794</v>
+        <v>78841</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444124</v>
+        <v>444093</v>
       </c>
       <c r="R52" t="n">
-        <v>6923712</v>
+        <v>6923866</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6455,7 +6446,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6465,7 +6456,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6496,45 +6487,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129926736</v>
+        <v>129926703</v>
       </c>
       <c r="B53" t="n">
-        <v>78841</v>
+        <v>98794</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444093</v>
+        <v>444124</v>
       </c>
       <c r="R53" t="n">
-        <v>6923866</v>
+        <v>6923712</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 58107-2025 artfynd.xlsx
+++ b/artfynd/A 58107-2025 artfynd.xlsx
@@ -2543,32 +2543,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129926722</v>
+        <v>129926723</v>
       </c>
       <c r="B18" t="n">
-        <v>92884</v>
+        <v>91875</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444366</v>
+        <v>444348</v>
       </c>
       <c r="R18" t="n">
-        <v>6924005</v>
+        <v>6924034</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2765,32 +2765,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129926723</v>
+        <v>129926722</v>
       </c>
       <c r="B20" t="n">
-        <v>91875</v>
+        <v>92884</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444348</v>
+        <v>444366</v>
       </c>
       <c r="R20" t="n">
-        <v>6924034</v>
+        <v>6924005</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3098,10 +3098,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129926707</v>
+        <v>129926727</v>
       </c>
       <c r="B23" t="n">
-        <v>78842</v>
+        <v>79674</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3109,21 +3109,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3133,13 +3133,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444272</v>
+        <v>444295</v>
       </c>
       <c r="R23" t="n">
-        <v>6923791</v>
+        <v>6923949</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3209,10 +3209,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129926727</v>
+        <v>129926707</v>
       </c>
       <c r="B24" t="n">
-        <v>79674</v>
+        <v>78842</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3220,21 +3220,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3244,13 +3244,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444295</v>
+        <v>444272</v>
       </c>
       <c r="R24" t="n">
-        <v>6923949</v>
+        <v>6923791</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3320,32 +3320,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129926714</v>
+        <v>129926731</v>
       </c>
       <c r="B25" t="n">
-        <v>91775</v>
+        <v>78842</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444331</v>
+        <v>444190</v>
       </c>
       <c r="R25" t="n">
-        <v>6923827</v>
+        <v>6923908</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3431,7 +3431,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129926731</v>
+        <v>129926700</v>
       </c>
       <c r="B26" t="n">
         <v>78842</v>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444190</v>
+        <v>444139</v>
       </c>
       <c r="R26" t="n">
-        <v>6923908</v>
+        <v>6923624</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3542,32 +3542,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129926700</v>
+        <v>129926714</v>
       </c>
       <c r="B27" t="n">
-        <v>78842</v>
+        <v>91775</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3577,10 +3577,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444139</v>
+        <v>444331</v>
       </c>
       <c r="R27" t="n">
-        <v>6923624</v>
+        <v>6923827</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3884,45 +3884,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129926696</v>
+        <v>129926729</v>
       </c>
       <c r="B30" t="n">
-        <v>80189</v>
+        <v>92884</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444018</v>
+        <v>444210</v>
       </c>
       <c r="R30" t="n">
-        <v>6923684</v>
+        <v>6923955</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3954,7 +3963,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3964,7 +3973,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3995,54 +4004,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129926729</v>
+        <v>129926696</v>
       </c>
       <c r="B31" t="n">
-        <v>92884</v>
+        <v>80189</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444210</v>
+        <v>444018</v>
       </c>
       <c r="R31" t="n">
-        <v>6923955</v>
+        <v>6923684</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4448,10 +4448,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129926698</v>
+        <v>129926697</v>
       </c>
       <c r="B35" t="n">
-        <v>79674</v>
+        <v>57737</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4459,34 +4459,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444118</v>
+        <v>444080</v>
       </c>
       <c r="R35" t="n">
-        <v>6923621</v>
+        <v>6923635</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4518,7 +4527,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4528,7 +4537,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4559,10 +4568,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129926697</v>
+        <v>129926698</v>
       </c>
       <c r="B36" t="n">
-        <v>57737</v>
+        <v>79674</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4570,43 +4579,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444080</v>
+        <v>444118</v>
       </c>
       <c r="R36" t="n">
-        <v>6923635</v>
+        <v>6923621</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5132,32 +5132,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129926721</v>
+        <v>129926720</v>
       </c>
       <c r="B41" t="n">
-        <v>79674</v>
+        <v>91775</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444365</v>
+        <v>444360</v>
       </c>
       <c r="R41" t="n">
-        <v>6923915</v>
+        <v>6923918</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5243,32 +5243,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129926720</v>
+        <v>129926721</v>
       </c>
       <c r="B42" t="n">
-        <v>91775</v>
+        <v>79674</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5278,10 +5278,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444360</v>
+        <v>444365</v>
       </c>
       <c r="R42" t="n">
-        <v>6923918</v>
+        <v>6923915</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6260,10 +6260,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129926713</v>
+        <v>129926736</v>
       </c>
       <c r="B51" t="n">
-        <v>91525</v>
+        <v>78841</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6271,21 +6271,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3242</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6295,13 +6295,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444347</v>
+        <v>444093</v>
       </c>
       <c r="R51" t="n">
-        <v>6923828</v>
+        <v>6923866</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6340,12 +6340,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Under grov, gammal nedfallen tallgren.</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6376,10 +6371,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129926736</v>
+        <v>129926713</v>
       </c>
       <c r="B52" t="n">
-        <v>78841</v>
+        <v>91525</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6387,21 +6382,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>3242</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6411,13 +6406,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444093</v>
+        <v>444347</v>
       </c>
       <c r="R52" t="n">
-        <v>6923866</v>
+        <v>6923828</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6446,7 +6441,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6456,7 +6451,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Under grov, gammal nedfallen tallgren.</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 58107-2025 artfynd.xlsx
+++ b/artfynd/A 58107-2025 artfynd.xlsx
@@ -2543,32 +2543,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129926723</v>
+        <v>129926725</v>
       </c>
       <c r="B18" t="n">
-        <v>91875</v>
+        <v>79706</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444348</v>
+        <v>444315</v>
       </c>
       <c r="R18" t="n">
-        <v>6924034</v>
+        <v>6923974</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2654,32 +2654,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129926725</v>
+        <v>129926723</v>
       </c>
       <c r="B19" t="n">
-        <v>79703</v>
+        <v>91878</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444315</v>
+        <v>444348</v>
       </c>
       <c r="R19" t="n">
-        <v>6923974</v>
+        <v>6924034</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2768,7 +2768,7 @@
         <v>129926722</v>
       </c>
       <c r="B20" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>129926699</v>
       </c>
       <c r="B21" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>129926738</v>
       </c>
       <c r="B22" t="n">
-        <v>80224</v>
+        <v>80227</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3098,10 +3098,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129926727</v>
+        <v>129926707</v>
       </c>
       <c r="B23" t="n">
-        <v>79674</v>
+        <v>78845</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3109,21 +3109,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3133,13 +3133,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444295</v>
+        <v>444272</v>
       </c>
       <c r="R23" t="n">
-        <v>6923949</v>
+        <v>6923791</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3209,10 +3209,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129926707</v>
+        <v>129926727</v>
       </c>
       <c r="B24" t="n">
-        <v>78842</v>
+        <v>79677</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3220,21 +3220,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3244,13 +3244,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444272</v>
+        <v>444295</v>
       </c>
       <c r="R24" t="n">
-        <v>6923791</v>
+        <v>6923949</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3323,7 +3323,7 @@
         <v>129926731</v>
       </c>
       <c r="B25" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>129926700</v>
       </c>
       <c r="B26" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>129926714</v>
       </c>
       <c r="B27" t="n">
-        <v>91775</v>
+        <v>91778</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3653,10 +3653,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129926726</v>
+        <v>129926737</v>
       </c>
       <c r="B28" t="n">
-        <v>57895</v>
+        <v>92925</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3664,37 +3664,46 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444309</v>
+        <v>444073</v>
       </c>
       <c r="R28" t="n">
-        <v>6923959</v>
+        <v>6923833</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3723,7 +3732,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3733,7 +3742,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3764,10 +3773,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129926737</v>
+        <v>129926726</v>
       </c>
       <c r="B29" t="n">
-        <v>92922</v>
+        <v>57898</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3775,46 +3784,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444073</v>
+        <v>444309</v>
       </c>
       <c r="R29" t="n">
-        <v>6923833</v>
+        <v>6923959</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3884,54 +3884,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129926729</v>
+        <v>129926696</v>
       </c>
       <c r="B30" t="n">
-        <v>92884</v>
+        <v>80192</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444210</v>
+        <v>444018</v>
       </c>
       <c r="R30" t="n">
-        <v>6923955</v>
+        <v>6923684</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3963,7 +3954,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3973,7 +3964,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4004,45 +3995,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129926696</v>
+        <v>129926729</v>
       </c>
       <c r="B31" t="n">
-        <v>80189</v>
+        <v>92887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444018</v>
+        <v>444210</v>
       </c>
       <c r="R31" t="n">
-        <v>6923684</v>
+        <v>6923955</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4115,45 +4115,54 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129926712</v>
+        <v>129926697</v>
       </c>
       <c r="B32" t="n">
-        <v>80224</v>
+        <v>57740</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444339</v>
+        <v>444080</v>
       </c>
       <c r="R32" t="n">
-        <v>6923809</v>
+        <v>6923635</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4185,7 +4194,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4195,7 +4204,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4229,7 +4238,7 @@
         <v>129926705</v>
       </c>
       <c r="B33" t="n">
-        <v>80224</v>
+        <v>80227</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4337,10 +4346,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129926718</v>
+        <v>129926712</v>
       </c>
       <c r="B34" t="n">
-        <v>97671</v>
+        <v>80227</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4348,21 +4357,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221941</v>
+        <v>6463</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4372,10 +4381,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444362</v>
+        <v>444339</v>
       </c>
       <c r="R34" t="n">
-        <v>6923872</v>
+        <v>6923809</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4407,7 +4416,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4417,7 +4426,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4448,54 +4457,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129926697</v>
+        <v>129926718</v>
       </c>
       <c r="B35" t="n">
-        <v>57737</v>
+        <v>97674</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444080</v>
+        <v>444362</v>
       </c>
       <c r="R35" t="n">
-        <v>6923635</v>
+        <v>6923872</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4571,7 +4571,7 @@
         <v>129926698</v>
       </c>
       <c r="B36" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>129926715</v>
       </c>
       <c r="B37" t="n">
-        <v>92244</v>
+        <v>92247</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>129926734</v>
       </c>
       <c r="B38" t="n">
-        <v>78750</v>
+        <v>78753</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>129926710</v>
       </c>
       <c r="B39" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>129926704</v>
       </c>
       <c r="B40" t="n">
-        <v>80225</v>
+        <v>80228</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5132,32 +5132,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129926720</v>
+        <v>129926721</v>
       </c>
       <c r="B41" t="n">
-        <v>91775</v>
+        <v>79677</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444360</v>
+        <v>444365</v>
       </c>
       <c r="R41" t="n">
-        <v>6923918</v>
+        <v>6923915</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5243,32 +5243,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129926721</v>
+        <v>129926720</v>
       </c>
       <c r="B42" t="n">
-        <v>79674</v>
+        <v>91778</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5278,10 +5278,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444365</v>
+        <v>444360</v>
       </c>
       <c r="R42" t="n">
-        <v>6923915</v>
+        <v>6923918</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5354,57 +5354,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129926706</v>
+        <v>129926724</v>
       </c>
       <c r="B43" t="n">
-        <v>90425</v>
+        <v>78845</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6286</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444279</v>
+        <v>444330</v>
       </c>
       <c r="R43" t="n">
-        <v>6923782</v>
+        <v>6923984</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5433,7 +5424,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5443,7 +5434,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5474,48 +5465,57 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129926724</v>
+        <v>129926706</v>
       </c>
       <c r="B44" t="n">
-        <v>78842</v>
+        <v>90428</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444330</v>
+        <v>444279</v>
       </c>
       <c r="R44" t="n">
-        <v>6923984</v>
+        <v>6923782</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5585,10 +5585,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129926728</v>
+        <v>129926709</v>
       </c>
       <c r="B45" t="n">
-        <v>91655</v>
+        <v>91528</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5596,21 +5596,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2079</v>
+        <v>3242</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5620,13 +5620,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444229</v>
+        <v>444268</v>
       </c>
       <c r="R45" t="n">
-        <v>6923882</v>
+        <v>6923829</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5696,48 +5696,57 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129926709</v>
+        <v>129926702</v>
       </c>
       <c r="B46" t="n">
-        <v>91525</v>
+        <v>98797</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3242</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444268</v>
+        <v>444122</v>
       </c>
       <c r="R46" t="n">
-        <v>6923829</v>
+        <v>6923680</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5766,7 +5775,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5776,7 +5785,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5807,54 +5816,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129926702</v>
+        <v>129926728</v>
       </c>
       <c r="B47" t="n">
-        <v>98794</v>
+        <v>91658</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444122</v>
+        <v>444229</v>
       </c>
       <c r="R47" t="n">
-        <v>6923680</v>
+        <v>6923882</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5930,7 +5930,7 @@
         <v>129926701</v>
       </c>
       <c r="B48" t="n">
-        <v>105860</v>
+        <v>105863</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6038,10 +6038,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129926730</v>
+        <v>129926733</v>
       </c>
       <c r="B49" t="n">
-        <v>78487</v>
+        <v>79677</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6049,21 +6049,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6073,10 +6073,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>444200</v>
+        <v>444163</v>
       </c>
       <c r="R49" t="n">
-        <v>6923914</v>
+        <v>6923898</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6149,10 +6149,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129926733</v>
+        <v>129926730</v>
       </c>
       <c r="B50" t="n">
-        <v>79674</v>
+        <v>78490</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6160,21 +6160,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6184,10 +6184,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444163</v>
+        <v>444200</v>
       </c>
       <c r="R50" t="n">
-        <v>6923898</v>
+        <v>6923914</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -6219,7 +6219,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6260,10 +6260,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129926736</v>
+        <v>129926713</v>
       </c>
       <c r="B51" t="n">
-        <v>78841</v>
+        <v>91528</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6271,21 +6271,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>3242</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6295,13 +6295,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444093</v>
+        <v>444347</v>
       </c>
       <c r="R51" t="n">
-        <v>6923866</v>
+        <v>6923828</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6340,7 +6340,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Under grov, gammal nedfallen tallgren.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6371,10 +6376,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129926713</v>
+        <v>129926736</v>
       </c>
       <c r="B52" t="n">
-        <v>91525</v>
+        <v>78844</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6382,21 +6387,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3242</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6406,13 +6411,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444347</v>
+        <v>444093</v>
       </c>
       <c r="R52" t="n">
-        <v>6923828</v>
+        <v>6923866</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6441,7 +6446,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6451,12 +6456,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Under grov, gammal nedfallen tallgren.</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6490,7 +6490,7 @@
         <v>129926703</v>
       </c>
       <c r="B53" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>129926717</v>
       </c>
       <c r="B54" t="n">
-        <v>91616</v>
+        <v>91619</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>129926735</v>
       </c>
       <c r="B55" t="n">
-        <v>91775</v>
+        <v>91778</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6829,32 +6829,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129926716</v>
+        <v>129926708</v>
       </c>
       <c r="B56" t="n">
-        <v>91775</v>
+        <v>79677</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6864,10 +6864,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444351</v>
+        <v>444257</v>
       </c>
       <c r="R56" t="n">
-        <v>6923878</v>
+        <v>6923818</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6909,7 +6909,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6940,32 +6940,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129926708</v>
+        <v>129926716</v>
       </c>
       <c r="B57" t="n">
-        <v>79674</v>
+        <v>91778</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6975,10 +6975,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>444257</v>
+        <v>444351</v>
       </c>
       <c r="R57" t="n">
-        <v>6923818</v>
+        <v>6923878</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7020,7 +7020,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 58107-2025 artfynd.xlsx
+++ b/artfynd/A 58107-2025 artfynd.xlsx
@@ -4115,54 +4115,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129926697</v>
+        <v>129926718</v>
       </c>
       <c r="B32" t="n">
-        <v>57740</v>
+        <v>97674</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444080</v>
+        <v>444362</v>
       </c>
       <c r="R32" t="n">
-        <v>6923635</v>
+        <v>6923872</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4194,7 +4185,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4204,7 +4195,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4235,48 +4226,57 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129926705</v>
+        <v>129926697</v>
       </c>
       <c r="B33" t="n">
-        <v>80227</v>
+        <v>57740</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444117</v>
+        <v>444080</v>
       </c>
       <c r="R33" t="n">
-        <v>6923735</v>
+        <v>6923635</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4346,7 +4346,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129926712</v>
+        <v>129926705</v>
       </c>
       <c r="B34" t="n">
         <v>80227</v>
@@ -4381,13 +4381,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444339</v>
+        <v>444117</v>
       </c>
       <c r="R34" t="n">
-        <v>6923809</v>
+        <v>6923735</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4457,10 +4457,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129926718</v>
+        <v>129926712</v>
       </c>
       <c r="B35" t="n">
-        <v>97674</v>
+        <v>80227</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4468,21 +4468,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221941</v>
+        <v>6463</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4492,10 +4492,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444362</v>
+        <v>444339</v>
       </c>
       <c r="R35" t="n">
-        <v>6923872</v>
+        <v>6923809</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5132,32 +5132,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129926721</v>
+        <v>129926720</v>
       </c>
       <c r="B41" t="n">
-        <v>79677</v>
+        <v>91778</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444365</v>
+        <v>444360</v>
       </c>
       <c r="R41" t="n">
-        <v>6923915</v>
+        <v>6923918</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5243,32 +5243,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129926720</v>
+        <v>129926721</v>
       </c>
       <c r="B42" t="n">
-        <v>91778</v>
+        <v>79677</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5278,10 +5278,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444360</v>
+        <v>444365</v>
       </c>
       <c r="R42" t="n">
-        <v>6923918</v>
+        <v>6923915</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 58107-2025 artfynd.xlsx
+++ b/artfynd/A 58107-2025 artfynd.xlsx
@@ -4901,10 +4901,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129926710</v>
+        <v>129926704</v>
       </c>
       <c r="B39" t="n">
-        <v>92887</v>
+        <v>80228</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4912,43 +4912,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444283</v>
+        <v>444124</v>
       </c>
       <c r="R39" t="n">
-        <v>6923819</v>
+        <v>6923727</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4980,7 +4971,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4990,7 +4981,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5021,10 +5012,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129926704</v>
+        <v>129926710</v>
       </c>
       <c r="B40" t="n">
-        <v>80228</v>
+        <v>92887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5032,34 +5023,43 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444124</v>
+        <v>444283</v>
       </c>
       <c r="R40" t="n">
-        <v>6923727</v>
+        <v>6923819</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6038,10 +6038,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129926733</v>
+        <v>129926730</v>
       </c>
       <c r="B49" t="n">
-        <v>79677</v>
+        <v>78490</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6049,21 +6049,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6073,10 +6073,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>444163</v>
+        <v>444200</v>
       </c>
       <c r="R49" t="n">
-        <v>6923898</v>
+        <v>6923914</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6149,10 +6149,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129926730</v>
+        <v>129926733</v>
       </c>
       <c r="B50" t="n">
-        <v>78490</v>
+        <v>79677</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6160,21 +6160,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6184,10 +6184,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444200</v>
+        <v>444163</v>
       </c>
       <c r="R50" t="n">
-        <v>6923914</v>
+        <v>6923898</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -6219,7 +6219,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 58107-2025 artfynd.xlsx
+++ b/artfynd/A 58107-2025 artfynd.xlsx
@@ -2543,32 +2543,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129926725</v>
+        <v>129926723</v>
       </c>
       <c r="B18" t="n">
-        <v>79706</v>
+        <v>91879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444315</v>
+        <v>444348</v>
       </c>
       <c r="R18" t="n">
-        <v>6923974</v>
+        <v>6924034</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2654,32 +2654,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129926723</v>
+        <v>129926725</v>
       </c>
       <c r="B19" t="n">
-        <v>91878</v>
+        <v>79707</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444348</v>
+        <v>444315</v>
       </c>
       <c r="R19" t="n">
-        <v>6924034</v>
+        <v>6923974</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2765,32 +2765,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129926722</v>
+        <v>129926699</v>
       </c>
       <c r="B20" t="n">
-        <v>92887</v>
+        <v>79678</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444366</v>
+        <v>444138</v>
       </c>
       <c r="R20" t="n">
-        <v>6924005</v>
+        <v>6923625</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2876,32 +2876,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129926699</v>
+        <v>129926722</v>
       </c>
       <c r="B21" t="n">
-        <v>79677</v>
+        <v>92888</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2911,10 +2911,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444138</v>
+        <v>444366</v>
       </c>
       <c r="R21" t="n">
-        <v>6923625</v>
+        <v>6924005</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2990,7 +2990,7 @@
         <v>129926738</v>
       </c>
       <c r="B22" t="n">
-        <v>80227</v>
+        <v>80228</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3098,10 +3098,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129926707</v>
+        <v>129926727</v>
       </c>
       <c r="B23" t="n">
-        <v>78845</v>
+        <v>79678</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3109,21 +3109,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3133,13 +3133,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444272</v>
+        <v>444295</v>
       </c>
       <c r="R23" t="n">
-        <v>6923791</v>
+        <v>6923949</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3209,10 +3209,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129926727</v>
+        <v>129926707</v>
       </c>
       <c r="B24" t="n">
-        <v>79677</v>
+        <v>78846</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3220,21 +3220,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3244,13 +3244,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444295</v>
+        <v>444272</v>
       </c>
       <c r="R24" t="n">
-        <v>6923949</v>
+        <v>6923791</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3320,32 +3320,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129926731</v>
+        <v>129926714</v>
       </c>
       <c r="B25" t="n">
-        <v>78845</v>
+        <v>91779</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444190</v>
+        <v>444331</v>
       </c>
       <c r="R25" t="n">
-        <v>6923908</v>
+        <v>6923827</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3431,10 +3431,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129926700</v>
+        <v>129926731</v>
       </c>
       <c r="B26" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444139</v>
+        <v>444190</v>
       </c>
       <c r="R26" t="n">
-        <v>6923624</v>
+        <v>6923908</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3542,32 +3542,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129926714</v>
+        <v>129926700</v>
       </c>
       <c r="B27" t="n">
-        <v>91778</v>
+        <v>78846</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3577,10 +3577,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444331</v>
+        <v>444139</v>
       </c>
       <c r="R27" t="n">
-        <v>6923827</v>
+        <v>6923624</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3656,7 +3656,7 @@
         <v>129926737</v>
       </c>
       <c r="B28" t="n">
-        <v>92925</v>
+        <v>92926</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3884,45 +3884,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129926696</v>
+        <v>129926729</v>
       </c>
       <c r="B30" t="n">
-        <v>80192</v>
+        <v>92888</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444018</v>
+        <v>444210</v>
       </c>
       <c r="R30" t="n">
-        <v>6923684</v>
+        <v>6923955</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3954,7 +3963,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3964,7 +3973,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3995,54 +4004,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129926729</v>
+        <v>129926696</v>
       </c>
       <c r="B31" t="n">
-        <v>92887</v>
+        <v>80193</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444210</v>
+        <v>444018</v>
       </c>
       <c r="R31" t="n">
-        <v>6923955</v>
+        <v>6923684</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4115,10 +4115,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129926718</v>
+        <v>129926712</v>
       </c>
       <c r="B32" t="n">
-        <v>97674</v>
+        <v>80228</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4126,21 +4126,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221941</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444362</v>
+        <v>444339</v>
       </c>
       <c r="R32" t="n">
-        <v>6923872</v>
+        <v>6923809</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4226,57 +4226,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129926697</v>
+        <v>129926705</v>
       </c>
       <c r="B33" t="n">
-        <v>57740</v>
+        <v>80228</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444080</v>
+        <v>444117</v>
       </c>
       <c r="R33" t="n">
-        <v>6923635</v>
+        <v>6923735</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4305,7 +4296,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4315,7 +4306,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4346,48 +4337,57 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129926705</v>
+        <v>129926697</v>
       </c>
       <c r="B34" t="n">
-        <v>80227</v>
+        <v>57740</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444117</v>
+        <v>444080</v>
       </c>
       <c r="R34" t="n">
-        <v>6923735</v>
+        <v>6923635</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4457,10 +4457,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129926712</v>
+        <v>129926718</v>
       </c>
       <c r="B35" t="n">
-        <v>80227</v>
+        <v>97675</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4468,21 +4468,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6463</v>
+        <v>221941</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4492,10 +4492,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444339</v>
+        <v>444362</v>
       </c>
       <c r="R35" t="n">
-        <v>6923809</v>
+        <v>6923872</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4571,7 +4571,7 @@
         <v>129926698</v>
       </c>
       <c r="B36" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>129926715</v>
       </c>
       <c r="B37" t="n">
-        <v>92247</v>
+        <v>92248</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>129926734</v>
       </c>
       <c r="B38" t="n">
-        <v>78753</v>
+        <v>78754</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>129926704</v>
       </c>
       <c r="B39" t="n">
-        <v>80228</v>
+        <v>80229</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         <v>129926710</v>
       </c>
       <c r="B40" t="n">
-        <v>92887</v>
+        <v>92888</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>129926720</v>
       </c>
       <c r="B41" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>129926721</v>
       </c>
       <c r="B42" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5354,48 +5354,57 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129926724</v>
+        <v>129926706</v>
       </c>
       <c r="B43" t="n">
-        <v>78845</v>
+        <v>90429</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444330</v>
+        <v>444279</v>
       </c>
       <c r="R43" t="n">
-        <v>6923984</v>
+        <v>6923782</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5424,7 +5433,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5434,7 +5443,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5465,57 +5474,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129926706</v>
+        <v>129926724</v>
       </c>
       <c r="B44" t="n">
-        <v>90428</v>
+        <v>78846</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6286</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444279</v>
+        <v>444330</v>
       </c>
       <c r="R44" t="n">
-        <v>6923782</v>
+        <v>6923984</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5585,10 +5585,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129926709</v>
+        <v>129926728</v>
       </c>
       <c r="B45" t="n">
-        <v>91528</v>
+        <v>91659</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5596,21 +5596,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3242</v>
+        <v>2079</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5620,13 +5620,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444268</v>
+        <v>444229</v>
       </c>
       <c r="R45" t="n">
-        <v>6923829</v>
+        <v>6923882</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5696,57 +5696,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129926702</v>
+        <v>129926709</v>
       </c>
       <c r="B46" t="n">
-        <v>98797</v>
+        <v>91529</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>3242</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444122</v>
+        <v>444268</v>
       </c>
       <c r="R46" t="n">
-        <v>6923680</v>
+        <v>6923829</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5775,7 +5766,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5785,7 +5776,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5816,32 +5807,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129926728</v>
+        <v>129926701</v>
       </c>
       <c r="B47" t="n">
-        <v>91658</v>
+        <v>105864</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2079</v>
+        <v>221144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5851,10 +5842,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444229</v>
+        <v>444126</v>
       </c>
       <c r="R47" t="n">
-        <v>6923882</v>
+        <v>6923694</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5886,7 +5877,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5896,7 +5887,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5927,45 +5918,54 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129926701</v>
+        <v>129926702</v>
       </c>
       <c r="B48" t="n">
-        <v>105863</v>
+        <v>98798</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444126</v>
+        <v>444122</v>
       </c>
       <c r="R48" t="n">
-        <v>6923694</v>
+        <v>6923680</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6041,7 +6041,7 @@
         <v>129926730</v>
       </c>
       <c r="B49" t="n">
-        <v>78490</v>
+        <v>78491</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>129926733</v>
       </c>
       <c r="B50" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6260,10 +6260,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129926713</v>
+        <v>129926736</v>
       </c>
       <c r="B51" t="n">
-        <v>91528</v>
+        <v>78845</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6271,21 +6271,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3242</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6295,13 +6295,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444347</v>
+        <v>444093</v>
       </c>
       <c r="R51" t="n">
-        <v>6923828</v>
+        <v>6923866</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6340,12 +6340,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Under grov, gammal nedfallen tallgren.</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6376,10 +6371,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129926736</v>
+        <v>129926713</v>
       </c>
       <c r="B52" t="n">
-        <v>78844</v>
+        <v>91529</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6387,21 +6382,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>3242</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6411,13 +6406,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444093</v>
+        <v>444347</v>
       </c>
       <c r="R52" t="n">
-        <v>6923866</v>
+        <v>6923828</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6446,7 +6441,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6456,7 +6451,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Under grov, gammal nedfallen tallgren.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6490,7 +6490,7 @@
         <v>129926703</v>
       </c>
       <c r="B53" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>129926717</v>
       </c>
       <c r="B54" t="n">
-        <v>91619</v>
+        <v>91620</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>129926735</v>
       </c>
       <c r="B55" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6829,32 +6829,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129926708</v>
+        <v>129926716</v>
       </c>
       <c r="B56" t="n">
-        <v>79677</v>
+        <v>91779</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6864,10 +6864,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444257</v>
+        <v>444351</v>
       </c>
       <c r="R56" t="n">
-        <v>6923818</v>
+        <v>6923878</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6909,7 +6909,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6940,32 +6940,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129926716</v>
+        <v>129926708</v>
       </c>
       <c r="B57" t="n">
-        <v>91778</v>
+        <v>79678</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6975,10 +6975,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>444351</v>
+        <v>444257</v>
       </c>
       <c r="R57" t="n">
-        <v>6923878</v>
+        <v>6923818</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7020,7 +7020,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 58107-2025 artfynd.xlsx
+++ b/artfynd/A 58107-2025 artfynd.xlsx
@@ -4337,10 +4337,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129926697</v>
+        <v>129926698</v>
       </c>
       <c r="B34" t="n">
-        <v>57740</v>
+        <v>79678</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4348,43 +4348,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444080</v>
+        <v>444118</v>
       </c>
       <c r="R34" t="n">
-        <v>6923635</v>
+        <v>6923621</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4416,7 +4407,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4426,7 +4417,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4457,45 +4448,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129926718</v>
+        <v>129926697</v>
       </c>
       <c r="B35" t="n">
-        <v>97675</v>
+        <v>57740</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444362</v>
+        <v>444080</v>
       </c>
       <c r="R35" t="n">
-        <v>6923872</v>
+        <v>6923635</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4568,32 +4568,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129926698</v>
+        <v>129926718</v>
       </c>
       <c r="B36" t="n">
-        <v>79678</v>
+        <v>97675</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>221941</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444118</v>
+        <v>444362</v>
       </c>
       <c r="R36" t="n">
-        <v>6923621</v>
+        <v>6923872</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4901,10 +4901,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129926704</v>
+        <v>129926710</v>
       </c>
       <c r="B39" t="n">
-        <v>80229</v>
+        <v>92888</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4912,34 +4912,43 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444124</v>
+        <v>444283</v>
       </c>
       <c r="R39" t="n">
-        <v>6923727</v>
+        <v>6923819</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4971,7 +4980,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4981,7 +4990,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5012,10 +5021,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129926710</v>
+        <v>129926704</v>
       </c>
       <c r="B40" t="n">
-        <v>92888</v>
+        <v>80229</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5023,43 +5032,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444283</v>
+        <v>444124</v>
       </c>
       <c r="R40" t="n">
-        <v>6923819</v>
+        <v>6923727</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5132,32 +5132,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129926720</v>
+        <v>129926721</v>
       </c>
       <c r="B41" t="n">
-        <v>91779</v>
+        <v>79678</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444360</v>
+        <v>444365</v>
       </c>
       <c r="R41" t="n">
-        <v>6923918</v>
+        <v>6923915</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5243,32 +5243,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129926721</v>
+        <v>129926720</v>
       </c>
       <c r="B42" t="n">
-        <v>79678</v>
+        <v>91779</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5278,10 +5278,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444365</v>
+        <v>444360</v>
       </c>
       <c r="R42" t="n">
-        <v>6923915</v>
+        <v>6923918</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 58107-2025 artfynd.xlsx
+++ b/artfynd/A 58107-2025 artfynd.xlsx
@@ -4337,10 +4337,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129926698</v>
+        <v>129926697</v>
       </c>
       <c r="B34" t="n">
-        <v>79678</v>
+        <v>57740</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4348,34 +4348,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444118</v>
+        <v>444080</v>
       </c>
       <c r="R34" t="n">
-        <v>6923621</v>
+        <v>6923635</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4407,7 +4416,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4417,7 +4426,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4448,54 +4457,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129926697</v>
+        <v>129926718</v>
       </c>
       <c r="B35" t="n">
-        <v>57740</v>
+        <v>97675</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444080</v>
+        <v>444362</v>
       </c>
       <c r="R35" t="n">
-        <v>6923635</v>
+        <v>6923872</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4568,32 +4568,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129926718</v>
+        <v>129926698</v>
       </c>
       <c r="B36" t="n">
-        <v>97675</v>
+        <v>79678</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221941</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444362</v>
+        <v>444118</v>
       </c>
       <c r="R36" t="n">
-        <v>6923872</v>
+        <v>6923621</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4901,10 +4901,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129926710</v>
+        <v>129926704</v>
       </c>
       <c r="B39" t="n">
-        <v>92888</v>
+        <v>80229</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4912,43 +4912,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444283</v>
+        <v>444124</v>
       </c>
       <c r="R39" t="n">
-        <v>6923819</v>
+        <v>6923727</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4980,7 +4971,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4990,7 +4981,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5021,10 +5012,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129926704</v>
+        <v>129926710</v>
       </c>
       <c r="B40" t="n">
-        <v>80229</v>
+        <v>92888</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5032,34 +5023,43 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444124</v>
+        <v>444283</v>
       </c>
       <c r="R40" t="n">
-        <v>6923727</v>
+        <v>6923819</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5132,32 +5132,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129926721</v>
+        <v>129926720</v>
       </c>
       <c r="B41" t="n">
-        <v>79678</v>
+        <v>91779</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444365</v>
+        <v>444360</v>
       </c>
       <c r="R41" t="n">
-        <v>6923915</v>
+        <v>6923918</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5243,32 +5243,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129926720</v>
+        <v>129926721</v>
       </c>
       <c r="B42" t="n">
-        <v>91779</v>
+        <v>79678</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5278,10 +5278,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444360</v>
+        <v>444365</v>
       </c>
       <c r="R42" t="n">
-        <v>6923918</v>
+        <v>6923915</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5585,32 +5585,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129926728</v>
+        <v>129926701</v>
       </c>
       <c r="B45" t="n">
-        <v>91659</v>
+        <v>105864</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2079</v>
+        <v>221144</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5620,10 +5620,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444229</v>
+        <v>444126</v>
       </c>
       <c r="R45" t="n">
-        <v>6923882</v>
+        <v>6923694</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5696,10 +5696,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129926709</v>
+        <v>129926728</v>
       </c>
       <c r="B46" t="n">
-        <v>91529</v>
+        <v>91659</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5707,21 +5707,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3242</v>
+        <v>2079</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5731,13 +5731,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444268</v>
+        <v>444229</v>
       </c>
       <c r="R46" t="n">
-        <v>6923829</v>
+        <v>6923882</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5807,32 +5807,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129926701</v>
+        <v>129926709</v>
       </c>
       <c r="B47" t="n">
-        <v>105864</v>
+        <v>91529</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>3242</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5842,13 +5842,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444126</v>
+        <v>444268</v>
       </c>
       <c r="R47" t="n">
-        <v>6923694</v>
+        <v>6923829</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6260,45 +6260,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129926736</v>
+        <v>129926703</v>
       </c>
       <c r="B51" t="n">
-        <v>78845</v>
+        <v>98798</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444093</v>
+        <v>444124</v>
       </c>
       <c r="R51" t="n">
-        <v>6923866</v>
+        <v>6923712</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6330,7 +6339,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6340,7 +6349,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6371,10 +6380,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129926713</v>
+        <v>129926736</v>
       </c>
       <c r="B52" t="n">
-        <v>91529</v>
+        <v>78845</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6382,21 +6391,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3242</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6406,13 +6415,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444347</v>
+        <v>444093</v>
       </c>
       <c r="R52" t="n">
-        <v>6923828</v>
+        <v>6923866</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6441,7 +6450,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6451,12 +6460,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Under grov, gammal nedfallen tallgren.</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6487,57 +6491,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129926703</v>
+        <v>129926713</v>
       </c>
       <c r="B53" t="n">
-        <v>98798</v>
+        <v>91529</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>3242</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444124</v>
+        <v>444347</v>
       </c>
       <c r="R53" t="n">
-        <v>6923712</v>
+        <v>6923828</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6566,7 +6561,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6576,7 +6571,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Under grov, gammal nedfallen tallgren.</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 58107-2025 artfynd.xlsx
+++ b/artfynd/A 58107-2025 artfynd.xlsx
@@ -2546,7 +2546,7 @@
         <v>129926723</v>
       </c>
       <c r="B18" t="n">
-        <v>91879</v>
+        <v>91896</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>129926725</v>
       </c>
       <c r="B19" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2765,32 +2765,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129926699</v>
+        <v>129926722</v>
       </c>
       <c r="B20" t="n">
-        <v>79678</v>
+        <v>92905</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444138</v>
+        <v>444366</v>
       </c>
       <c r="R20" t="n">
-        <v>6923625</v>
+        <v>6924005</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2876,32 +2876,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129926722</v>
+        <v>129926699</v>
       </c>
       <c r="B21" t="n">
-        <v>92888</v>
+        <v>79679</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2911,10 +2911,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444366</v>
+        <v>444138</v>
       </c>
       <c r="R21" t="n">
-        <v>6924005</v>
+        <v>6923625</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2990,7 +2990,7 @@
         <v>129926738</v>
       </c>
       <c r="B22" t="n">
-        <v>80228</v>
+        <v>80229</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3098,10 +3098,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129926727</v>
+        <v>129926707</v>
       </c>
       <c r="B23" t="n">
-        <v>79678</v>
+        <v>78847</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3109,21 +3109,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3133,13 +3133,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444295</v>
+        <v>444272</v>
       </c>
       <c r="R23" t="n">
-        <v>6923949</v>
+        <v>6923791</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3209,10 +3209,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129926707</v>
+        <v>129926727</v>
       </c>
       <c r="B24" t="n">
-        <v>78846</v>
+        <v>79679</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3220,21 +3220,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3244,13 +3244,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444272</v>
+        <v>444295</v>
       </c>
       <c r="R24" t="n">
-        <v>6923791</v>
+        <v>6923949</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3320,32 +3320,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129926714</v>
+        <v>129926731</v>
       </c>
       <c r="B25" t="n">
-        <v>91779</v>
+        <v>78847</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444331</v>
+        <v>444190</v>
       </c>
       <c r="R25" t="n">
-        <v>6923827</v>
+        <v>6923908</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3431,10 +3431,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129926731</v>
+        <v>129926700</v>
       </c>
       <c r="B26" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444190</v>
+        <v>444139</v>
       </c>
       <c r="R26" t="n">
-        <v>6923908</v>
+        <v>6923624</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3542,32 +3542,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129926700</v>
+        <v>129926714</v>
       </c>
       <c r="B27" t="n">
-        <v>78846</v>
+        <v>91796</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3577,10 +3577,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444139</v>
+        <v>444331</v>
       </c>
       <c r="R27" t="n">
-        <v>6923624</v>
+        <v>6923827</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3656,7 +3656,7 @@
         <v>129926737</v>
       </c>
       <c r="B28" t="n">
-        <v>92926</v>
+        <v>92943</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>129926726</v>
       </c>
       <c r="B29" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>129926729</v>
       </c>
       <c r="B30" t="n">
-        <v>92888</v>
+        <v>92905</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>129926696</v>
       </c>
       <c r="B31" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>129926712</v>
       </c>
       <c r="B32" t="n">
-        <v>80228</v>
+        <v>80229</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>129926705</v>
       </c>
       <c r="B33" t="n">
-        <v>80228</v>
+        <v>80229</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>129926718</v>
       </c>
       <c r="B35" t="n">
-        <v>97675</v>
+        <v>97692</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>129926698</v>
       </c>
       <c r="B36" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>129926715</v>
       </c>
       <c r="B37" t="n">
-        <v>92248</v>
+        <v>92265</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>129926734</v>
       </c>
       <c r="B38" t="n">
-        <v>78754</v>
+        <v>78755</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>129926704</v>
       </c>
       <c r="B39" t="n">
-        <v>80229</v>
+        <v>80230</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         <v>129926710</v>
       </c>
       <c r="B40" t="n">
-        <v>92888</v>
+        <v>92905</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>129926720</v>
       </c>
       <c r="B41" t="n">
-        <v>91779</v>
+        <v>91796</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>129926721</v>
       </c>
       <c r="B42" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>129926706</v>
       </c>
       <c r="B43" t="n">
-        <v>90429</v>
+        <v>90446</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>129926724</v>
       </c>
       <c r="B44" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5585,32 +5585,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129926701</v>
+        <v>129926709</v>
       </c>
       <c r="B45" t="n">
-        <v>105864</v>
+        <v>91546</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221144</v>
+        <v>3242</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5620,13 +5620,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444126</v>
+        <v>444268</v>
       </c>
       <c r="R45" t="n">
-        <v>6923694</v>
+        <v>6923829</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5696,45 +5696,54 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129926728</v>
+        <v>129926702</v>
       </c>
       <c r="B46" t="n">
-        <v>91659</v>
+        <v>98815</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444229</v>
+        <v>444122</v>
       </c>
       <c r="R46" t="n">
-        <v>6923882</v>
+        <v>6923680</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5766,7 +5775,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5776,7 +5785,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5807,32 +5816,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129926709</v>
+        <v>129926701</v>
       </c>
       <c r="B47" t="n">
-        <v>91529</v>
+        <v>105881</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3242</v>
+        <v>221144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5842,13 +5851,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444268</v>
+        <v>444126</v>
       </c>
       <c r="R47" t="n">
-        <v>6923829</v>
+        <v>6923694</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5877,7 +5886,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5887,7 +5896,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5918,54 +5927,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129926702</v>
+        <v>129926728</v>
       </c>
       <c r="B48" t="n">
-        <v>98798</v>
+        <v>91676</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444122</v>
+        <v>444229</v>
       </c>
       <c r="R48" t="n">
-        <v>6923680</v>
+        <v>6923882</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5997,7 +5997,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6041,7 +6041,7 @@
         <v>129926730</v>
       </c>
       <c r="B49" t="n">
-        <v>78491</v>
+        <v>78492</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>129926733</v>
       </c>
       <c r="B50" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6260,57 +6260,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129926703</v>
+        <v>129926713</v>
       </c>
       <c r="B51" t="n">
-        <v>98798</v>
+        <v>91546</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>3242</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444124</v>
+        <v>444347</v>
       </c>
       <c r="R51" t="n">
-        <v>6923712</v>
+        <v>6923828</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6339,7 +6330,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6349,7 +6340,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Under grov, gammal nedfallen tallgren.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6383,7 +6379,7 @@
         <v>129926736</v>
       </c>
       <c r="B52" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6491,48 +6487,57 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129926713</v>
+        <v>129926703</v>
       </c>
       <c r="B53" t="n">
-        <v>91529</v>
+        <v>98815</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3242</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444347</v>
+        <v>444124</v>
       </c>
       <c r="R53" t="n">
-        <v>6923828</v>
+        <v>6923712</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6561,7 +6566,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6571,12 +6576,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Under grov, gammal nedfallen tallgren.</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6610,7 +6610,7 @@
         <v>129926717</v>
       </c>
       <c r="B54" t="n">
-        <v>91620</v>
+        <v>91637</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>129926735</v>
       </c>
       <c r="B55" t="n">
-        <v>91779</v>
+        <v>91796</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
         <v>129926716</v>
       </c>
       <c r="B56" t="n">
-        <v>91779</v>
+        <v>91796</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>129926708</v>
       </c>
       <c r="B57" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 58107-2025 artfynd.xlsx
+++ b/artfynd/A 58107-2025 artfynd.xlsx
@@ -4115,10 +4115,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129926712</v>
+        <v>129926718</v>
       </c>
       <c r="B32" t="n">
-        <v>80235</v>
+        <v>97708</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4126,21 +4126,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6463</v>
+        <v>221941</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444339</v>
+        <v>444362</v>
       </c>
       <c r="R32" t="n">
-        <v>6923809</v>
+        <v>6923872</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4226,7 +4226,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129926705</v>
+        <v>129926712</v>
       </c>
       <c r="B33" t="n">
         <v>80235</v>
@@ -4261,13 +4261,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444117</v>
+        <v>444339</v>
       </c>
       <c r="R33" t="n">
-        <v>6923735</v>
+        <v>6923809</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4337,57 +4337,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129926697</v>
+        <v>129926705</v>
       </c>
       <c r="B34" t="n">
-        <v>57741</v>
+        <v>80235</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444080</v>
+        <v>444117</v>
       </c>
       <c r="R34" t="n">
-        <v>6923635</v>
+        <v>6923735</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4416,7 +4407,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4426,7 +4417,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4457,10 +4448,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129926698</v>
+        <v>129926697</v>
       </c>
       <c r="B35" t="n">
-        <v>79685</v>
+        <v>57741</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4468,34 +4459,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444118</v>
+        <v>444080</v>
       </c>
       <c r="R35" t="n">
-        <v>6923621</v>
+        <v>6923635</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4568,32 +4568,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129926718</v>
+        <v>129926698</v>
       </c>
       <c r="B36" t="n">
-        <v>97708</v>
+        <v>79685</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221941</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444362</v>
+        <v>444118</v>
       </c>
       <c r="R36" t="n">
-        <v>6923872</v>
+        <v>6923621</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 58107-2025 artfynd.xlsx
+++ b/artfynd/A 58107-2025 artfynd.xlsx
@@ -2546,7 +2546,7 @@
         <v>129926723</v>
       </c>
       <c r="B18" t="n">
-        <v>91912</v>
+        <v>91914</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>129926722</v>
       </c>
       <c r="B19" t="n">
-        <v>92921</v>
+        <v>92923</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2987,32 +2987,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129926738</v>
+        <v>129926727</v>
       </c>
       <c r="B22" t="n">
-        <v>80235</v>
+        <v>79685</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3022,13 +3022,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444051</v>
+        <v>444295</v>
       </c>
       <c r="R22" t="n">
-        <v>6923830</v>
+        <v>6923949</v>
       </c>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3098,32 +3098,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129926727</v>
+        <v>129926738</v>
       </c>
       <c r="B23" t="n">
-        <v>79685</v>
+        <v>80235</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3133,13 +3133,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444295</v>
+        <v>444051</v>
       </c>
       <c r="R23" t="n">
-        <v>6923949</v>
+        <v>6923830</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3320,32 +3320,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129926731</v>
+        <v>129926714</v>
       </c>
       <c r="B25" t="n">
-        <v>78853</v>
+        <v>91814</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444190</v>
+        <v>444331</v>
       </c>
       <c r="R25" t="n">
-        <v>6923908</v>
+        <v>6923827</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3431,7 +3431,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129926700</v>
+        <v>129926731</v>
       </c>
       <c r="B26" t="n">
         <v>78853</v>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444139</v>
+        <v>444190</v>
       </c>
       <c r="R26" t="n">
-        <v>6923624</v>
+        <v>6923908</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3542,32 +3542,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129926714</v>
+        <v>129926700</v>
       </c>
       <c r="B27" t="n">
-        <v>91812</v>
+        <v>78853</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3577,10 +3577,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444331</v>
+        <v>444139</v>
       </c>
       <c r="R27" t="n">
-        <v>6923827</v>
+        <v>6923624</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3653,10 +3653,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129926737</v>
+        <v>129926726</v>
       </c>
       <c r="B28" t="n">
-        <v>92959</v>
+        <v>57900</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3664,46 +3664,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444073</v>
+        <v>444309</v>
       </c>
       <c r="R28" t="n">
-        <v>6923833</v>
+        <v>6923959</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3732,7 +3723,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3742,7 +3733,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3773,10 +3764,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129926726</v>
+        <v>129926737</v>
       </c>
       <c r="B29" t="n">
-        <v>57900</v>
+        <v>92961</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3784,37 +3775,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444309</v>
+        <v>444073</v>
       </c>
       <c r="R29" t="n">
-        <v>6923959</v>
+        <v>6923833</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3887,7 +3887,7 @@
         <v>129926729</v>
       </c>
       <c r="B30" t="n">
-        <v>92921</v>
+        <v>92923</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4115,45 +4115,54 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129926718</v>
+        <v>129926697</v>
       </c>
       <c r="B32" t="n">
-        <v>97708</v>
+        <v>57741</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444362</v>
+        <v>444080</v>
       </c>
       <c r="R32" t="n">
-        <v>6923872</v>
+        <v>6923635</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4185,7 +4194,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4195,7 +4204,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4448,54 +4457,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129926697</v>
+        <v>129926718</v>
       </c>
       <c r="B35" t="n">
-        <v>57741</v>
+        <v>97710</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444080</v>
+        <v>444362</v>
       </c>
       <c r="R35" t="n">
-        <v>6923635</v>
+        <v>6923872</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4682,7 +4682,7 @@
         <v>129926715</v>
       </c>
       <c r="B37" t="n">
-        <v>92281</v>
+        <v>92283</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>129926710</v>
       </c>
       <c r="B39" t="n">
-        <v>92921</v>
+        <v>92923</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5132,32 +5132,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129926720</v>
+        <v>129926721</v>
       </c>
       <c r="B41" t="n">
-        <v>91812</v>
+        <v>79685</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444360</v>
+        <v>444365</v>
       </c>
       <c r="R41" t="n">
-        <v>6923918</v>
+        <v>6923915</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5243,32 +5243,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129926721</v>
+        <v>129926720</v>
       </c>
       <c r="B42" t="n">
-        <v>79685</v>
+        <v>91814</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5278,10 +5278,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444365</v>
+        <v>444360</v>
       </c>
       <c r="R42" t="n">
-        <v>6923915</v>
+        <v>6923918</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5357,7 +5357,7 @@
         <v>129926706</v>
       </c>
       <c r="B43" t="n">
-        <v>90462</v>
+        <v>90464</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5585,32 +5585,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129926701</v>
+        <v>129926728</v>
       </c>
       <c r="B45" t="n">
-        <v>105897</v>
+        <v>91694</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221144</v>
+        <v>2079</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5620,10 +5620,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444126</v>
+        <v>444229</v>
       </c>
       <c r="R45" t="n">
-        <v>6923694</v>
+        <v>6923882</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5696,10 +5696,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129926728</v>
+        <v>129926709</v>
       </c>
       <c r="B46" t="n">
-        <v>91692</v>
+        <v>91564</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5707,21 +5707,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2079</v>
+        <v>3242</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5731,13 +5731,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444229</v>
+        <v>444268</v>
       </c>
       <c r="R46" t="n">
-        <v>6923882</v>
+        <v>6923829</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5807,48 +5807,57 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129926709</v>
+        <v>129926702</v>
       </c>
       <c r="B47" t="n">
-        <v>91562</v>
+        <v>98833</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3242</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444268</v>
+        <v>444122</v>
       </c>
       <c r="R47" t="n">
-        <v>6923829</v>
+        <v>6923680</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5877,7 +5886,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5887,7 +5896,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5918,54 +5927,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129926702</v>
+        <v>129926701</v>
       </c>
       <c r="B48" t="n">
-        <v>98831</v>
+        <v>105900</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444122</v>
+        <v>444126</v>
       </c>
       <c r="R48" t="n">
-        <v>6923680</v>
+        <v>6923694</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6263,7 +6263,7 @@
         <v>129926713</v>
       </c>
       <c r="B51" t="n">
-        <v>91562</v>
+        <v>91564</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>129926703</v>
       </c>
       <c r="B53" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>129926717</v>
       </c>
       <c r="B54" t="n">
-        <v>91653</v>
+        <v>91655</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>129926735</v>
       </c>
       <c r="B55" t="n">
-        <v>91812</v>
+        <v>91814</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
         <v>129926716</v>
       </c>
       <c r="B56" t="n">
-        <v>91812</v>
+        <v>91814</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 58107-2025 artfynd.xlsx
+++ b/artfynd/A 58107-2025 artfynd.xlsx
@@ -2543,32 +2543,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129926723</v>
+        <v>129926699</v>
       </c>
       <c r="B18" t="n">
-        <v>91914</v>
+        <v>79770</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>65</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444348</v>
+        <v>444138</v>
       </c>
       <c r="R18" t="n">
-        <v>6924034</v>
+        <v>6923625</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2654,32 +2654,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129926722</v>
+        <v>129926725</v>
       </c>
       <c r="B19" t="n">
-        <v>92923</v>
+        <v>79799</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444366</v>
+        <v>444315</v>
       </c>
       <c r="R19" t="n">
-        <v>6924005</v>
+        <v>6923974</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2765,32 +2765,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129926725</v>
+        <v>129926723</v>
       </c>
       <c r="B20" t="n">
-        <v>79714</v>
+        <v>92001</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444315</v>
+        <v>444348</v>
       </c>
       <c r="R20" t="n">
-        <v>6923974</v>
+        <v>6924034</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2876,32 +2876,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129926699</v>
+        <v>129926722</v>
       </c>
       <c r="B21" t="n">
-        <v>79685</v>
+        <v>93010</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2911,10 +2911,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444138</v>
+        <v>444366</v>
       </c>
       <c r="R21" t="n">
-        <v>6923625</v>
+        <v>6924005</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2987,32 +2987,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129926727</v>
+        <v>129926738</v>
       </c>
       <c r="B22" t="n">
-        <v>79685</v>
+        <v>80320</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3022,13 +3022,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444295</v>
+        <v>444051</v>
       </c>
       <c r="R22" t="n">
-        <v>6923949</v>
+        <v>6923830</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3098,32 +3098,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129926738</v>
+        <v>129926707</v>
       </c>
       <c r="B23" t="n">
-        <v>80235</v>
+        <v>78938</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3133,13 +3133,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444051</v>
+        <v>444272</v>
       </c>
       <c r="R23" t="n">
-        <v>6923830</v>
+        <v>6923791</v>
       </c>
       <c r="S23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3209,10 +3209,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129926707</v>
+        <v>129926727</v>
       </c>
       <c r="B24" t="n">
-        <v>78853</v>
+        <v>79770</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3220,21 +3220,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3244,13 +3244,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444272</v>
+        <v>444295</v>
       </c>
       <c r="R24" t="n">
-        <v>6923791</v>
+        <v>6923949</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3323,7 +3323,7 @@
         <v>129926714</v>
       </c>
       <c r="B25" t="n">
-        <v>91814</v>
+        <v>91901</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>129926731</v>
       </c>
       <c r="B26" t="n">
-        <v>78853</v>
+        <v>78938</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>129926700</v>
       </c>
       <c r="B27" t="n">
-        <v>78853</v>
+        <v>78938</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>129926726</v>
       </c>
       <c r="B28" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>129926737</v>
       </c>
       <c r="B29" t="n">
-        <v>92961</v>
+        <v>93048</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>129926729</v>
       </c>
       <c r="B30" t="n">
-        <v>92923</v>
+        <v>93010</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>129926696</v>
       </c>
       <c r="B31" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>129926697</v>
       </c>
       <c r="B32" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4235,32 +4235,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129926712</v>
+        <v>129926698</v>
       </c>
       <c r="B33" t="n">
-        <v>80235</v>
+        <v>79770</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6463</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4270,10 +4270,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444339</v>
+        <v>444118</v>
       </c>
       <c r="R33" t="n">
-        <v>6923809</v>
+        <v>6923621</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4349,7 +4349,7 @@
         <v>129926705</v>
       </c>
       <c r="B34" t="n">
-        <v>80235</v>
+        <v>80320</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4457,10 +4457,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129926718</v>
+        <v>129926712</v>
       </c>
       <c r="B35" t="n">
-        <v>97710</v>
+        <v>80320</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4468,21 +4468,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221941</v>
+        <v>6463</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4492,10 +4492,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444362</v>
+        <v>444339</v>
       </c>
       <c r="R35" t="n">
-        <v>6923872</v>
+        <v>6923809</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4568,32 +4568,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129926698</v>
+        <v>129926718</v>
       </c>
       <c r="B36" t="n">
-        <v>79685</v>
+        <v>97797</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>221941</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444118</v>
+        <v>444362</v>
       </c>
       <c r="R36" t="n">
-        <v>6923621</v>
+        <v>6923872</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4682,7 +4682,7 @@
         <v>129926715</v>
       </c>
       <c r="B37" t="n">
-        <v>92283</v>
+        <v>92370</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>129926734</v>
       </c>
       <c r="B38" t="n">
-        <v>78761</v>
+        <v>78846</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4901,10 +4901,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129926710</v>
+        <v>129926704</v>
       </c>
       <c r="B39" t="n">
-        <v>92923</v>
+        <v>80321</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4912,43 +4912,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444283</v>
+        <v>444124</v>
       </c>
       <c r="R39" t="n">
-        <v>6923819</v>
+        <v>6923727</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4980,7 +4971,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4990,7 +4981,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5021,10 +5012,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129926704</v>
+        <v>129926710</v>
       </c>
       <c r="B40" t="n">
-        <v>80236</v>
+        <v>93010</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5032,34 +5023,43 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444124</v>
+        <v>444283</v>
       </c>
       <c r="R40" t="n">
-        <v>6923727</v>
+        <v>6923819</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5132,32 +5132,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129926721</v>
+        <v>129926720</v>
       </c>
       <c r="B41" t="n">
-        <v>79685</v>
+        <v>91901</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444365</v>
+        <v>444360</v>
       </c>
       <c r="R41" t="n">
-        <v>6923915</v>
+        <v>6923918</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5243,32 +5243,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129926720</v>
+        <v>129926721</v>
       </c>
       <c r="B42" t="n">
-        <v>91814</v>
+        <v>79770</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5278,10 +5278,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444360</v>
+        <v>444365</v>
       </c>
       <c r="R42" t="n">
-        <v>6923918</v>
+        <v>6923915</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5354,57 +5354,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129926706</v>
+        <v>129926724</v>
       </c>
       <c r="B43" t="n">
-        <v>90464</v>
+        <v>78938</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6286</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444279</v>
+        <v>444330</v>
       </c>
       <c r="R43" t="n">
-        <v>6923782</v>
+        <v>6923984</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5433,7 +5424,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5443,7 +5434,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5474,48 +5465,57 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129926724</v>
+        <v>129926706</v>
       </c>
       <c r="B44" t="n">
-        <v>78853</v>
+        <v>90539</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444330</v>
+        <v>444279</v>
       </c>
       <c r="R44" t="n">
-        <v>6923984</v>
+        <v>6923782</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5588,7 +5588,7 @@
         <v>129926728</v>
       </c>
       <c r="B45" t="n">
-        <v>91694</v>
+        <v>91781</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5696,48 +5696,57 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129926709</v>
+        <v>129926702</v>
       </c>
       <c r="B46" t="n">
-        <v>91564</v>
+        <v>98920</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3242</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444268</v>
+        <v>444122</v>
       </c>
       <c r="R46" t="n">
-        <v>6923829</v>
+        <v>6923680</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5766,7 +5775,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5776,7 +5785,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5807,57 +5816,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129926702</v>
+        <v>129926709</v>
       </c>
       <c r="B47" t="n">
-        <v>98833</v>
+        <v>91651</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>3242</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444122</v>
+        <v>444268</v>
       </c>
       <c r="R47" t="n">
-        <v>6923680</v>
+        <v>6923829</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5930,7 +5930,7 @@
         <v>129926701</v>
       </c>
       <c r="B48" t="n">
-        <v>105900</v>
+        <v>105987</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>129926730</v>
       </c>
       <c r="B49" t="n">
-        <v>78498</v>
+        <v>78583</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>129926733</v>
       </c>
       <c r="B50" t="n">
-        <v>79685</v>
+        <v>79770</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>129926713</v>
       </c>
       <c r="B51" t="n">
-        <v>91564</v>
+        <v>91651</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6376,45 +6376,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129926736</v>
+        <v>129926703</v>
       </c>
       <c r="B52" t="n">
-        <v>78852</v>
+        <v>98920</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444093</v>
+        <v>444124</v>
       </c>
       <c r="R52" t="n">
-        <v>6923866</v>
+        <v>6923712</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6446,7 +6455,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6456,7 +6465,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6487,54 +6496,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129926703</v>
+        <v>129926736</v>
       </c>
       <c r="B53" t="n">
-        <v>98833</v>
+        <v>78937</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444124</v>
+        <v>444093</v>
       </c>
       <c r="R53" t="n">
-        <v>6923712</v>
+        <v>6923866</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6610,7 +6610,7 @@
         <v>129926717</v>
       </c>
       <c r="B54" t="n">
-        <v>91655</v>
+        <v>91742</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>129926735</v>
       </c>
       <c r="B55" t="n">
-        <v>91814</v>
+        <v>91901</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6829,32 +6829,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129926716</v>
+        <v>129926708</v>
       </c>
       <c r="B56" t="n">
-        <v>91814</v>
+        <v>79770</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6864,10 +6864,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444351</v>
+        <v>444257</v>
       </c>
       <c r="R56" t="n">
-        <v>6923878</v>
+        <v>6923818</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6909,7 +6909,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6940,32 +6940,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129926708</v>
+        <v>129926716</v>
       </c>
       <c r="B57" t="n">
-        <v>79685</v>
+        <v>91901</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6975,10 +6975,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>444257</v>
+        <v>444351</v>
       </c>
       <c r="R57" t="n">
-        <v>6923818</v>
+        <v>6923878</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7020,7 +7020,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 58107-2025 artfynd.xlsx
+++ b/artfynd/A 58107-2025 artfynd.xlsx
@@ -2543,32 +2543,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129926699</v>
+        <v>129926723</v>
       </c>
       <c r="B18" t="n">
-        <v>79770</v>
+        <v>92001</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>65</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444138</v>
+        <v>444348</v>
       </c>
       <c r="R18" t="n">
-        <v>6923625</v>
+        <v>6924034</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2654,32 +2654,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129926725</v>
+        <v>129926722</v>
       </c>
       <c r="B19" t="n">
-        <v>79799</v>
+        <v>93010</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444315</v>
+        <v>444366</v>
       </c>
       <c r="R19" t="n">
-        <v>6923974</v>
+        <v>6924005</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2765,32 +2765,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129926723</v>
+        <v>129926699</v>
       </c>
       <c r="B20" t="n">
-        <v>92001</v>
+        <v>79770</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>65</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444348</v>
+        <v>444138</v>
       </c>
       <c r="R20" t="n">
-        <v>6924034</v>
+        <v>6923625</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2876,32 +2876,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129926722</v>
+        <v>129926725</v>
       </c>
       <c r="B21" t="n">
-        <v>93010</v>
+        <v>79799</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2911,10 +2911,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444366</v>
+        <v>444315</v>
       </c>
       <c r="R21" t="n">
-        <v>6924005</v>
+        <v>6923974</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4901,10 +4901,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129926704</v>
+        <v>129926710</v>
       </c>
       <c r="B39" t="n">
-        <v>80321</v>
+        <v>93010</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4912,34 +4912,43 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444124</v>
+        <v>444283</v>
       </c>
       <c r="R39" t="n">
-        <v>6923727</v>
+        <v>6923819</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4971,7 +4980,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4981,7 +4990,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5012,10 +5021,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129926710</v>
+        <v>129926704</v>
       </c>
       <c r="B40" t="n">
-        <v>93010</v>
+        <v>80321</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5023,43 +5032,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444283</v>
+        <v>444124</v>
       </c>
       <c r="R40" t="n">
-        <v>6923819</v>
+        <v>6923727</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 58107-2025 artfynd.xlsx
+++ b/artfynd/A 58107-2025 artfynd.xlsx
@@ -2543,32 +2543,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129926723</v>
+        <v>129926699</v>
       </c>
       <c r="B18" t="n">
-        <v>92001</v>
+        <v>79770</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>65</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444348</v>
+        <v>444138</v>
       </c>
       <c r="R18" t="n">
-        <v>6924034</v>
+        <v>6923625</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2654,32 +2654,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129926722</v>
+        <v>129926725</v>
       </c>
       <c r="B19" t="n">
-        <v>93010</v>
+        <v>79799</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444366</v>
+        <v>444315</v>
       </c>
       <c r="R19" t="n">
-        <v>6924005</v>
+        <v>6923974</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2765,32 +2765,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129926699</v>
+        <v>129926723</v>
       </c>
       <c r="B20" t="n">
-        <v>79770</v>
+        <v>92001</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>65</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444138</v>
+        <v>444348</v>
       </c>
       <c r="R20" t="n">
-        <v>6923625</v>
+        <v>6924034</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2876,32 +2876,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129926725</v>
+        <v>129926722</v>
       </c>
       <c r="B21" t="n">
-        <v>79799</v>
+        <v>93010</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2911,10 +2911,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444315</v>
+        <v>444366</v>
       </c>
       <c r="R21" t="n">
-        <v>6923974</v>
+        <v>6924005</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4901,10 +4901,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129926710</v>
+        <v>129926704</v>
       </c>
       <c r="B39" t="n">
-        <v>93010</v>
+        <v>80321</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4912,43 +4912,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444283</v>
+        <v>444124</v>
       </c>
       <c r="R39" t="n">
-        <v>6923819</v>
+        <v>6923727</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4980,7 +4971,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4990,7 +4981,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5021,10 +5012,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129926704</v>
+        <v>129926710</v>
       </c>
       <c r="B40" t="n">
-        <v>80321</v>
+        <v>93010</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5032,34 +5023,43 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444124</v>
+        <v>444283</v>
       </c>
       <c r="R40" t="n">
-        <v>6923727</v>
+        <v>6923819</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5585,45 +5585,54 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129926728</v>
+        <v>129926702</v>
       </c>
       <c r="B45" t="n">
-        <v>91781</v>
+        <v>98920</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444229</v>
+        <v>444122</v>
       </c>
       <c r="R45" t="n">
-        <v>6923882</v>
+        <v>6923680</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5655,7 +5664,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5665,7 +5674,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5696,57 +5705,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129926702</v>
+        <v>129926709</v>
       </c>
       <c r="B46" t="n">
-        <v>98920</v>
+        <v>91651</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>3242</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444122</v>
+        <v>444268</v>
       </c>
       <c r="R46" t="n">
-        <v>6923680</v>
+        <v>6923829</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5816,32 +5816,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129926709</v>
+        <v>129926701</v>
       </c>
       <c r="B47" t="n">
-        <v>91651</v>
+        <v>105987</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3242</v>
+        <v>221144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444268</v>
+        <v>444126</v>
       </c>
       <c r="R47" t="n">
-        <v>6923829</v>
+        <v>6923694</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5927,32 +5927,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129926701</v>
+        <v>129926728</v>
       </c>
       <c r="B48" t="n">
-        <v>105987</v>
+        <v>91781</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221144</v>
+        <v>2079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5962,10 +5962,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444126</v>
+        <v>444229</v>
       </c>
       <c r="R48" t="n">
-        <v>6923694</v>
+        <v>6923882</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5997,7 +5997,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 58107-2025 artfynd.xlsx
+++ b/artfynd/A 58107-2025 artfynd.xlsx
@@ -2543,32 +2543,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129926699</v>
+        <v>129926723</v>
       </c>
       <c r="B18" t="n">
-        <v>79770</v>
+        <v>92001</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>65</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444138</v>
+        <v>444348</v>
       </c>
       <c r="R18" t="n">
-        <v>6923625</v>
+        <v>6924034</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2765,32 +2765,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129926723</v>
+        <v>129926722</v>
       </c>
       <c r="B20" t="n">
-        <v>92001</v>
+        <v>93010</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444348</v>
+        <v>444366</v>
       </c>
       <c r="R20" t="n">
-        <v>6924034</v>
+        <v>6924005</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2876,32 +2876,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129926722</v>
+        <v>129926699</v>
       </c>
       <c r="B21" t="n">
-        <v>93010</v>
+        <v>79770</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2911,10 +2911,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444366</v>
+        <v>444138</v>
       </c>
       <c r="R21" t="n">
-        <v>6924005</v>
+        <v>6923625</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3098,10 +3098,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129926707</v>
+        <v>129926727</v>
       </c>
       <c r="B23" t="n">
-        <v>78938</v>
+        <v>79770</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3109,21 +3109,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3133,13 +3133,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444272</v>
+        <v>444295</v>
       </c>
       <c r="R23" t="n">
-        <v>6923791</v>
+        <v>6923949</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3209,10 +3209,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129926727</v>
+        <v>129926707</v>
       </c>
       <c r="B24" t="n">
-        <v>79770</v>
+        <v>78938</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3220,21 +3220,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3244,13 +3244,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444295</v>
+        <v>444272</v>
       </c>
       <c r="R24" t="n">
-        <v>6923949</v>
+        <v>6923791</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3653,10 +3653,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129926726</v>
+        <v>129926737</v>
       </c>
       <c r="B28" t="n">
-        <v>57985</v>
+        <v>93048</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3664,37 +3664,46 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444309</v>
+        <v>444073</v>
       </c>
       <c r="R28" t="n">
-        <v>6923959</v>
+        <v>6923833</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3723,7 +3732,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3733,7 +3742,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3764,10 +3773,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129926737</v>
+        <v>129926726</v>
       </c>
       <c r="B29" t="n">
-        <v>93048</v>
+        <v>57985</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3775,46 +3784,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444073</v>
+        <v>444309</v>
       </c>
       <c r="R29" t="n">
-        <v>6923833</v>
+        <v>6923959</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3884,54 +3884,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129926729</v>
+        <v>129926696</v>
       </c>
       <c r="B30" t="n">
-        <v>93010</v>
+        <v>80285</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444210</v>
+        <v>444018</v>
       </c>
       <c r="R30" t="n">
-        <v>6923955</v>
+        <v>6923684</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3963,7 +3954,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3973,7 +3964,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4004,45 +3995,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129926696</v>
+        <v>129926729</v>
       </c>
       <c r="B31" t="n">
-        <v>80285</v>
+        <v>93010</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444018</v>
+        <v>444210</v>
       </c>
       <c r="R31" t="n">
-        <v>6923684</v>
+        <v>6923955</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4115,54 +4115,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129926697</v>
+        <v>129926718</v>
       </c>
       <c r="B32" t="n">
-        <v>57826</v>
+        <v>97797</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444080</v>
+        <v>444362</v>
       </c>
       <c r="R32" t="n">
-        <v>6923635</v>
+        <v>6923872</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4194,7 +4185,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4204,7 +4195,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4235,32 +4226,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129926698</v>
+        <v>129926712</v>
       </c>
       <c r="B33" t="n">
-        <v>79770</v>
+        <v>80320</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>6463</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4270,10 +4261,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444118</v>
+        <v>444339</v>
       </c>
       <c r="R33" t="n">
-        <v>6923621</v>
+        <v>6923809</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4305,7 +4296,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4315,7 +4306,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4457,45 +4448,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129926712</v>
+        <v>129926697</v>
       </c>
       <c r="B35" t="n">
-        <v>80320</v>
+        <v>57826</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444339</v>
+        <v>444080</v>
       </c>
       <c r="R35" t="n">
-        <v>6923809</v>
+        <v>6923635</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4568,32 +4568,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129926718</v>
+        <v>129926698</v>
       </c>
       <c r="B36" t="n">
-        <v>97797</v>
+        <v>79770</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221941</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444362</v>
+        <v>444118</v>
       </c>
       <c r="R36" t="n">
-        <v>6923872</v>
+        <v>6923621</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5354,48 +5354,57 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129926724</v>
+        <v>129926706</v>
       </c>
       <c r="B43" t="n">
-        <v>78938</v>
+        <v>90538</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444330</v>
+        <v>444279</v>
       </c>
       <c r="R43" t="n">
-        <v>6923984</v>
+        <v>6923782</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5424,7 +5433,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5434,7 +5443,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5465,57 +5474,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129926706</v>
+        <v>129926724</v>
       </c>
       <c r="B44" t="n">
-        <v>90539</v>
+        <v>78938</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6286</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444279</v>
+        <v>444330</v>
       </c>
       <c r="R44" t="n">
-        <v>6923782</v>
+        <v>6923984</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5585,57 +5585,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129926702</v>
+        <v>129926709</v>
       </c>
       <c r="B45" t="n">
-        <v>98920</v>
+        <v>91651</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>3242</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444122</v>
+        <v>444268</v>
       </c>
       <c r="R45" t="n">
-        <v>6923680</v>
+        <v>6923829</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5664,7 +5655,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5674,7 +5665,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5705,10 +5696,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129926709</v>
+        <v>129926728</v>
       </c>
       <c r="B46" t="n">
-        <v>91651</v>
+        <v>91781</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5716,21 +5707,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3242</v>
+        <v>2079</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5740,13 +5731,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444268</v>
+        <v>444229</v>
       </c>
       <c r="R46" t="n">
-        <v>6923829</v>
+        <v>6923882</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5775,7 +5766,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5785,7 +5776,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5816,45 +5807,54 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129926701</v>
+        <v>129926702</v>
       </c>
       <c r="B47" t="n">
-        <v>105987</v>
+        <v>98920</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444126</v>
+        <v>444122</v>
       </c>
       <c r="R47" t="n">
-        <v>6923694</v>
+        <v>6923680</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5927,32 +5927,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129926728</v>
+        <v>129926701</v>
       </c>
       <c r="B48" t="n">
-        <v>91781</v>
+        <v>105987</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2079</v>
+        <v>221144</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5962,10 +5962,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444229</v>
+        <v>444126</v>
       </c>
       <c r="R48" t="n">
-        <v>6923882</v>
+        <v>6923694</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5997,7 +5997,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6038,10 +6038,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129926730</v>
+        <v>129926733</v>
       </c>
       <c r="B49" t="n">
-        <v>78583</v>
+        <v>79770</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6049,21 +6049,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6073,10 +6073,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>444200</v>
+        <v>444163</v>
       </c>
       <c r="R49" t="n">
-        <v>6923914</v>
+        <v>6923898</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6149,10 +6149,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129926733</v>
+        <v>129926730</v>
       </c>
       <c r="B50" t="n">
-        <v>79770</v>
+        <v>78583</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6160,21 +6160,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6184,10 +6184,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444163</v>
+        <v>444200</v>
       </c>
       <c r="R50" t="n">
-        <v>6923898</v>
+        <v>6923914</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -6219,7 +6219,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6376,54 +6376,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129926703</v>
+        <v>129926736</v>
       </c>
       <c r="B52" t="n">
-        <v>98920</v>
+        <v>78937</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444124</v>
+        <v>444093</v>
       </c>
       <c r="R52" t="n">
-        <v>6923712</v>
+        <v>6923866</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6455,7 +6446,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6465,7 +6456,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6496,45 +6487,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129926736</v>
+        <v>129926703</v>
       </c>
       <c r="B53" t="n">
-        <v>78937</v>
+        <v>98920</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444093</v>
+        <v>444124</v>
       </c>
       <c r="R53" t="n">
-        <v>6923866</v>
+        <v>6923712</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6829,32 +6829,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129926708</v>
+        <v>129926716</v>
       </c>
       <c r="B56" t="n">
-        <v>79770</v>
+        <v>91901</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6864,10 +6864,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444257</v>
+        <v>444351</v>
       </c>
       <c r="R56" t="n">
-        <v>6923818</v>
+        <v>6923878</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6909,7 +6909,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6940,32 +6940,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129926716</v>
+        <v>129926708</v>
       </c>
       <c r="B57" t="n">
-        <v>91901</v>
+        <v>79770</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6975,10 +6975,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>444351</v>
+        <v>444257</v>
       </c>
       <c r="R57" t="n">
-        <v>6923878</v>
+        <v>6923818</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7020,7 +7020,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 58107-2025 artfynd.xlsx
+++ b/artfynd/A 58107-2025 artfynd.xlsx
@@ -2543,32 +2543,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129926723</v>
+        <v>129926725</v>
       </c>
       <c r="B18" t="n">
-        <v>92001</v>
+        <v>79799</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444348</v>
+        <v>444315</v>
       </c>
       <c r="R18" t="n">
-        <v>6924034</v>
+        <v>6923974</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2654,32 +2654,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129926725</v>
+        <v>129926723</v>
       </c>
       <c r="B19" t="n">
-        <v>79799</v>
+        <v>92001</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444315</v>
+        <v>444348</v>
       </c>
       <c r="R19" t="n">
-        <v>6923974</v>
+        <v>6924034</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -4115,45 +4115,54 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129926718</v>
+        <v>129926697</v>
       </c>
       <c r="B32" t="n">
-        <v>97797</v>
+        <v>57826</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444362</v>
+        <v>444080</v>
       </c>
       <c r="R32" t="n">
-        <v>6923872</v>
+        <v>6923635</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4185,7 +4194,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4195,7 +4204,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4448,54 +4457,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129926697</v>
+        <v>129926718</v>
       </c>
       <c r="B35" t="n">
-        <v>57826</v>
+        <v>97797</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444080</v>
+        <v>444362</v>
       </c>
       <c r="R35" t="n">
-        <v>6923635</v>
+        <v>6923872</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5585,10 +5585,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129926709</v>
+        <v>129926728</v>
       </c>
       <c r="B45" t="n">
-        <v>91651</v>
+        <v>91781</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5596,21 +5596,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3242</v>
+        <v>2079</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5620,13 +5620,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444268</v>
+        <v>444229</v>
       </c>
       <c r="R45" t="n">
-        <v>6923829</v>
+        <v>6923882</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5696,10 +5696,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129926728</v>
+        <v>129926709</v>
       </c>
       <c r="B46" t="n">
-        <v>91781</v>
+        <v>91651</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5707,21 +5707,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2079</v>
+        <v>3242</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5731,13 +5731,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444229</v>
+        <v>444268</v>
       </c>
       <c r="R46" t="n">
-        <v>6923882</v>
+        <v>6923829</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5807,54 +5807,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129926702</v>
+        <v>129926701</v>
       </c>
       <c r="B47" t="n">
-        <v>98920</v>
+        <v>105987</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444122</v>
+        <v>444126</v>
       </c>
       <c r="R47" t="n">
-        <v>6923680</v>
+        <v>6923694</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5927,45 +5918,54 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129926701</v>
+        <v>129926702</v>
       </c>
       <c r="B48" t="n">
-        <v>105987</v>
+        <v>98920</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444126</v>
+        <v>444122</v>
       </c>
       <c r="R48" t="n">
-        <v>6923694</v>
+        <v>6923680</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6038,10 +6038,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129926733</v>
+        <v>129926730</v>
       </c>
       <c r="B49" t="n">
-        <v>79770</v>
+        <v>78583</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6049,21 +6049,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6073,10 +6073,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>444163</v>
+        <v>444200</v>
       </c>
       <c r="R49" t="n">
-        <v>6923898</v>
+        <v>6923914</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6149,10 +6149,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129926730</v>
+        <v>129926733</v>
       </c>
       <c r="B50" t="n">
-        <v>78583</v>
+        <v>79770</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6160,21 +6160,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6184,10 +6184,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444200</v>
+        <v>444163</v>
       </c>
       <c r="R50" t="n">
-        <v>6923914</v>
+        <v>6923898</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -6219,7 +6219,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6376,45 +6376,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129926736</v>
+        <v>129926703</v>
       </c>
       <c r="B52" t="n">
-        <v>78937</v>
+        <v>98920</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444093</v>
+        <v>444124</v>
       </c>
       <c r="R52" t="n">
-        <v>6923866</v>
+        <v>6923712</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6446,7 +6455,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6456,7 +6465,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6487,54 +6496,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129926703</v>
+        <v>129926736</v>
       </c>
       <c r="B53" t="n">
-        <v>98920</v>
+        <v>78937</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444124</v>
+        <v>444093</v>
       </c>
       <c r="R53" t="n">
-        <v>6923712</v>
+        <v>6923866</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6829,32 +6829,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129926716</v>
+        <v>129926708</v>
       </c>
       <c r="B56" t="n">
-        <v>91901</v>
+        <v>79770</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6864,10 +6864,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444351</v>
+        <v>444257</v>
       </c>
       <c r="R56" t="n">
-        <v>6923878</v>
+        <v>6923818</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6909,7 +6909,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6940,32 +6940,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129926708</v>
+        <v>129926716</v>
       </c>
       <c r="B57" t="n">
-        <v>79770</v>
+        <v>91901</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6975,10 +6975,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>444257</v>
+        <v>444351</v>
       </c>
       <c r="R57" t="n">
-        <v>6923818</v>
+        <v>6923878</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7020,7 +7020,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 58107-2025 artfynd.xlsx
+++ b/artfynd/A 58107-2025 artfynd.xlsx
@@ -2543,32 +2543,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129926725</v>
+        <v>129926723</v>
       </c>
       <c r="B18" t="n">
-        <v>79799</v>
+        <v>91914</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444315</v>
+        <v>444348</v>
       </c>
       <c r="R18" t="n">
-        <v>6923974</v>
+        <v>6924034</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2654,32 +2654,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129926723</v>
+        <v>129926722</v>
       </c>
       <c r="B19" t="n">
-        <v>92001</v>
+        <v>92923</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444348</v>
+        <v>444366</v>
       </c>
       <c r="R19" t="n">
-        <v>6924034</v>
+        <v>6924005</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2765,32 +2765,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129926722</v>
+        <v>129926725</v>
       </c>
       <c r="B20" t="n">
-        <v>93010</v>
+        <v>79714</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444366</v>
+        <v>444315</v>
       </c>
       <c r="R20" t="n">
-        <v>6924005</v>
+        <v>6923974</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2879,7 +2879,7 @@
         <v>129926699</v>
       </c>
       <c r="B21" t="n">
-        <v>79770</v>
+        <v>79685</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2987,32 +2987,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129926738</v>
+        <v>129926727</v>
       </c>
       <c r="B22" t="n">
-        <v>80320</v>
+        <v>79685</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3022,13 +3022,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444051</v>
+        <v>444295</v>
       </c>
       <c r="R22" t="n">
-        <v>6923830</v>
+        <v>6923949</v>
       </c>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3098,32 +3098,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129926727</v>
+        <v>129926738</v>
       </c>
       <c r="B23" t="n">
-        <v>79770</v>
+        <v>80235</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3133,13 +3133,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444295</v>
+        <v>444051</v>
       </c>
       <c r="R23" t="n">
-        <v>6923949</v>
+        <v>6923830</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3212,7 +3212,7 @@
         <v>129926707</v>
       </c>
       <c r="B24" t="n">
-        <v>78938</v>
+        <v>78853</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>129926714</v>
       </c>
       <c r="B25" t="n">
-        <v>91901</v>
+        <v>91814</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>129926731</v>
       </c>
       <c r="B26" t="n">
-        <v>78938</v>
+        <v>78853</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>129926700</v>
       </c>
       <c r="B27" t="n">
-        <v>78938</v>
+        <v>78853</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3653,10 +3653,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129926737</v>
+        <v>129926726</v>
       </c>
       <c r="B28" t="n">
-        <v>93048</v>
+        <v>57900</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3664,46 +3664,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444073</v>
+        <v>444309</v>
       </c>
       <c r="R28" t="n">
-        <v>6923833</v>
+        <v>6923959</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3732,7 +3723,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3742,7 +3733,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3773,10 +3764,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129926726</v>
+        <v>129926737</v>
       </c>
       <c r="B29" t="n">
-        <v>57985</v>
+        <v>92961</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3784,37 +3775,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444309</v>
+        <v>444073</v>
       </c>
       <c r="R29" t="n">
-        <v>6923959</v>
+        <v>6923833</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3884,45 +3884,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129926696</v>
+        <v>129926729</v>
       </c>
       <c r="B30" t="n">
-        <v>80285</v>
+        <v>92923</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444018</v>
+        <v>444210</v>
       </c>
       <c r="R30" t="n">
-        <v>6923684</v>
+        <v>6923955</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3954,7 +3963,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3964,7 +3973,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3995,54 +4004,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129926729</v>
+        <v>129926696</v>
       </c>
       <c r="B31" t="n">
-        <v>93010</v>
+        <v>80200</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444210</v>
+        <v>444018</v>
       </c>
       <c r="R31" t="n">
-        <v>6923955</v>
+        <v>6923684</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4118,7 +4118,7 @@
         <v>129926697</v>
       </c>
       <c r="B32" t="n">
-        <v>57826</v>
+        <v>57741</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>129926712</v>
       </c>
       <c r="B33" t="n">
-        <v>80320</v>
+        <v>80235</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>129926705</v>
       </c>
       <c r="B34" t="n">
-        <v>80320</v>
+        <v>80235</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>129926718</v>
       </c>
       <c r="B35" t="n">
-        <v>97797</v>
+        <v>97710</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>129926698</v>
       </c>
       <c r="B36" t="n">
-        <v>79770</v>
+        <v>79685</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>129926715</v>
       </c>
       <c r="B37" t="n">
-        <v>92370</v>
+        <v>92283</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>129926734</v>
       </c>
       <c r="B38" t="n">
-        <v>78846</v>
+        <v>78761</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4901,10 +4901,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129926704</v>
+        <v>129926710</v>
       </c>
       <c r="B39" t="n">
-        <v>80321</v>
+        <v>92923</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4912,34 +4912,43 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444124</v>
+        <v>444283</v>
       </c>
       <c r="R39" t="n">
-        <v>6923727</v>
+        <v>6923819</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4971,7 +4980,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4981,7 +4990,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5012,10 +5021,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129926710</v>
+        <v>129926704</v>
       </c>
       <c r="B40" t="n">
-        <v>93010</v>
+        <v>80236</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5023,43 +5032,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444283</v>
+        <v>444124</v>
       </c>
       <c r="R40" t="n">
-        <v>6923819</v>
+        <v>6923727</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5132,32 +5132,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129926720</v>
+        <v>129926721</v>
       </c>
       <c r="B41" t="n">
-        <v>91901</v>
+        <v>79685</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444360</v>
+        <v>444365</v>
       </c>
       <c r="R41" t="n">
-        <v>6923918</v>
+        <v>6923915</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5243,32 +5243,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129926721</v>
+        <v>129926720</v>
       </c>
       <c r="B42" t="n">
-        <v>79770</v>
+        <v>91814</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5278,10 +5278,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444365</v>
+        <v>444360</v>
       </c>
       <c r="R42" t="n">
-        <v>6923915</v>
+        <v>6923918</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5357,7 +5357,7 @@
         <v>129926706</v>
       </c>
       <c r="B43" t="n">
-        <v>90538</v>
+        <v>90464</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>129926724</v>
       </c>
       <c r="B44" t="n">
-        <v>78938</v>
+        <v>78853</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5588,7 +5588,7 @@
         <v>129926728</v>
       </c>
       <c r="B45" t="n">
-        <v>91781</v>
+        <v>91694</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>129926709</v>
       </c>
       <c r="B46" t="n">
-        <v>91651</v>
+        <v>91564</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5807,45 +5807,54 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129926701</v>
+        <v>129926702</v>
       </c>
       <c r="B47" t="n">
-        <v>105987</v>
+        <v>98833</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444126</v>
+        <v>444122</v>
       </c>
       <c r="R47" t="n">
-        <v>6923694</v>
+        <v>6923680</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5918,54 +5927,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129926702</v>
+        <v>129926701</v>
       </c>
       <c r="B48" t="n">
-        <v>98920</v>
+        <v>105900</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444122</v>
+        <v>444126</v>
       </c>
       <c r="R48" t="n">
-        <v>6923680</v>
+        <v>6923694</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6041,7 +6041,7 @@
         <v>129926730</v>
       </c>
       <c r="B49" t="n">
-        <v>78583</v>
+        <v>78498</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>129926733</v>
       </c>
       <c r="B50" t="n">
-        <v>79770</v>
+        <v>79685</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>129926713</v>
       </c>
       <c r="B51" t="n">
-        <v>91651</v>
+        <v>91564</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6376,54 +6376,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129926703</v>
+        <v>129926736</v>
       </c>
       <c r="B52" t="n">
-        <v>98920</v>
+        <v>78852</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444124</v>
+        <v>444093</v>
       </c>
       <c r="R52" t="n">
-        <v>6923712</v>
+        <v>6923866</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6455,7 +6446,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6465,7 +6456,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6496,45 +6487,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129926736</v>
+        <v>129926703</v>
       </c>
       <c r="B53" t="n">
-        <v>78937</v>
+        <v>98833</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444093</v>
+        <v>444124</v>
       </c>
       <c r="R53" t="n">
-        <v>6923866</v>
+        <v>6923712</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6610,7 +6610,7 @@
         <v>129926717</v>
       </c>
       <c r="B54" t="n">
-        <v>91742</v>
+        <v>91655</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>129926735</v>
       </c>
       <c r="B55" t="n">
-        <v>91901</v>
+        <v>91814</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6829,32 +6829,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129926708</v>
+        <v>129926716</v>
       </c>
       <c r="B56" t="n">
-        <v>79770</v>
+        <v>91814</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6864,10 +6864,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444257</v>
+        <v>444351</v>
       </c>
       <c r="R56" t="n">
-        <v>6923818</v>
+        <v>6923878</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6909,7 +6909,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6940,32 +6940,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129926716</v>
+        <v>129926708</v>
       </c>
       <c r="B57" t="n">
-        <v>91901</v>
+        <v>79685</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6975,10 +6975,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>444351</v>
+        <v>444257</v>
       </c>
       <c r="R57" t="n">
-        <v>6923878</v>
+        <v>6923818</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7020,7 +7020,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 58107-2025 artfynd.xlsx
+++ b/artfynd/A 58107-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119385865</v>
+        <v>129926723</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,43 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Järpbäcken, Järpbäcken, Hjd</t>
+          <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444049</v>
+        <v>444348</v>
       </c>
       <c r="R2" t="n">
-        <v>6923640</v>
+        <v>6924034</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +770,7 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -792,19 +778,18 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119385475</v>
+        <v>119385161</v>
       </c>
       <c r="B3" t="n">
-        <v>91259</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92637</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444009</v>
+        <v>443985</v>
       </c>
       <c r="R3" t="n">
-        <v>6923747</v>
+        <v>6923818</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,37 +893,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119385416</v>
+        <v>119385475</v>
       </c>
       <c r="B4" t="n">
-        <v>97811</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92637</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220093</v>
+        <v>67</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444008</v>
+        <v>444009</v>
       </c>
       <c r="R4" t="n">
-        <v>6923751</v>
+        <v>6923747</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -983,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,37 +1000,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119386274</v>
+        <v>119385432</v>
       </c>
       <c r="B5" t="n">
-        <v>94311</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2809</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444085</v>
+        <v>444008</v>
       </c>
       <c r="R5" t="n">
-        <v>6923692</v>
+        <v>6923751</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1095,7 +1070,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1080,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,6 +1091,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Dead wood # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1132,59 +1127,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119386491</v>
+        <v>129926734</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Järpbäcken, Järpbäcken, Hjd</t>
+          <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444066</v>
+        <v>444169</v>
       </c>
       <c r="R6" t="n">
-        <v>6923830</v>
+        <v>6923886</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1211,22 +1192,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,7 +1222,7 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -1249,19 +1230,18 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>119386001</v>
       </c>
       <c r="B7" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,15 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119386464</v>
+        <v>129926717</v>
       </c>
       <c r="B8" t="n">
-        <v>90712</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,34 +1356,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1503</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Järpbäcken, Järpbäcken, Hjd</t>
+          <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444184</v>
+        <v>444352</v>
       </c>
       <c r="R8" t="n">
-        <v>6923782</v>
+        <v>6923879</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1435,22 +1410,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,7 +1440,7 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -1473,19 +1448,18 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119386311</v>
+        <v>119386464</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,43 +1467,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Järpbäcken, Järpbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444071</v>
+        <v>444184</v>
       </c>
       <c r="R9" t="n">
-        <v>6923737</v>
+        <v>6923782</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1561,7 +1526,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1536,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,59 +1563,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119386444</v>
+        <v>129926714</v>
       </c>
       <c r="B10" t="n">
-        <v>108526</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220204</v>
+        <v>1503</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Järpbäcken, Järpbäcken, Hjd</t>
+          <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444191</v>
+        <v>444331</v>
       </c>
       <c r="R10" t="n">
-        <v>6923760</v>
+        <v>6923827</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1677,22 +1628,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,7 +1658,7 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -1715,63 +1666,53 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119386449</v>
+        <v>129926716</v>
       </c>
       <c r="B11" t="n">
-        <v>108526</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220204</v>
+        <v>1503</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Järpbäcken, Järpbäcken, Hjd</t>
+          <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444184</v>
+        <v>444351</v>
       </c>
       <c r="R11" t="n">
-        <v>6923782</v>
+        <v>6923878</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1798,22 +1739,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,7 +1769,7 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -1836,54 +1777,53 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119385353</v>
+        <v>129926720</v>
       </c>
       <c r="B12" t="n">
-        <v>89964</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5685</v>
+        <v>1503</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Järpbäcken, Järpbäcken, Hjd</t>
+          <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444017</v>
+        <v>444360</v>
       </c>
       <c r="R12" t="n">
-        <v>6923752</v>
+        <v>6923918</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1910,22 +1850,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,7 +1880,7 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -1948,66 +1888,56 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119386422</v>
+        <v>129926735</v>
       </c>
       <c r="B13" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>1503</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Järpbäcken, Järpbäcken, Hjd</t>
+          <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>444060</v>
+        <v>444143</v>
       </c>
       <c r="R13" t="n">
-        <v>6923853</v>
+        <v>6923881</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2031,22 +1961,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,7 +1991,7 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -2069,54 +1999,53 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119386336</v>
+        <v>129926728</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Järpbäcken, Järpbäcken, Hjd</t>
+          <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444060</v>
+        <v>444229</v>
       </c>
       <c r="R14" t="n">
-        <v>6923853</v>
+        <v>6923882</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2143,22 +2072,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,7 +2102,7 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -2181,41 +2110,40 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119385327</v>
+        <v>119385016</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2225,10 +2153,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444017</v>
+        <v>443985</v>
       </c>
       <c r="R15" t="n">
-        <v>6923752</v>
+        <v>6923818</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2260,7 +2188,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2270,7 +2198,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2297,37 +2225,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119385432</v>
+        <v>119386274</v>
       </c>
       <c r="B16" t="n">
-        <v>74630</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>308</v>
+        <v>2809</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2337,10 +2260,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444008</v>
+        <v>444085</v>
       </c>
       <c r="R16" t="n">
-        <v>6923751</v>
+        <v>6923692</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2372,7 +2295,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2382,7 +2305,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2393,26 +2316,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Dead wood # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2429,64 +2332,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119395143</v>
+        <v>129926709</v>
       </c>
       <c r="B17" t="n">
-        <v>86354</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3624</v>
+        <v>3242</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Järpbäcken, Hjd</t>
+          <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444039</v>
+        <v>444268</v>
       </c>
       <c r="R17" t="n">
-        <v>6923661</v>
+        <v>6923829</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2510,12 +2397,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2524,14 +2421,13 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -2539,36 +2435,40 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129926723</v>
+        <v>129926713</v>
       </c>
       <c r="B18" t="n">
-        <v>92001</v>
+        <v>91831</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>65</v>
+        <v>3242</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2578,10 +2478,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444348</v>
+        <v>444347</v>
       </c>
       <c r="R18" t="n">
-        <v>6924034</v>
+        <v>6923828</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2613,7 +2513,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2623,7 +2523,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Under grov, gammal nedfallen tallgren.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2654,10 +2559,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129926722</v>
+        <v>119395143</v>
       </c>
       <c r="B19" t="n">
-        <v>93010</v>
+        <v>87412</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2665,34 +2570,41 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>3624</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Högfjället, Hjd</t>
+          <t>Järpbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444366</v>
+        <v>444039</v>
       </c>
       <c r="R19" t="n">
-        <v>6924005</v>
+        <v>6923661</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2719,22 +2631,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10:45</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>10:45</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2743,13 +2645,14 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -2757,18 +2660,14 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Mellanskog AB - Högfjället</t>
-        </is>
-      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129926725</v>
+        <v>119386422</v>
       </c>
       <c r="B20" t="n">
-        <v>79799</v>
+        <v>93191</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2776,34 +2675,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Högfjället, Hjd</t>
+          <t>Järpbäcken, Järpbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444315</v>
+        <v>444060</v>
       </c>
       <c r="R20" t="n">
-        <v>6923974</v>
+        <v>6923853</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2830,22 +2738,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2860,7 +2768,7 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -2868,18 +2776,14 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Mellanskog AB - Högfjället</t>
-        </is>
-      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129926699</v>
+        <v>129926710</v>
       </c>
       <c r="B21" t="n">
-        <v>79770</v>
+        <v>93197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2887,34 +2791,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444138</v>
+        <v>444283</v>
       </c>
       <c r="R21" t="n">
-        <v>6923625</v>
+        <v>6923819</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2946,7 +2859,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2956,7 +2869,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2987,32 +2900,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129926738</v>
+        <v>129926722</v>
       </c>
       <c r="B22" t="n">
-        <v>80320</v>
+        <v>93197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3022,13 +2935,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444051</v>
+        <v>444366</v>
       </c>
       <c r="R22" t="n">
-        <v>6923830</v>
+        <v>6924005</v>
       </c>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3057,7 +2970,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3067,7 +2980,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3098,10 +3011,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129926727</v>
+        <v>129926729</v>
       </c>
       <c r="B23" t="n">
-        <v>79770</v>
+        <v>93197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3109,37 +3022,46 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444295</v>
+        <v>444210</v>
       </c>
       <c r="R23" t="n">
-        <v>6923949</v>
+        <v>6923955</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3168,7 +3090,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3178,7 +3100,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3209,10 +3131,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129926707</v>
+        <v>129926715</v>
       </c>
       <c r="B24" t="n">
-        <v>78938</v>
+        <v>92556</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3220,21 +3142,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>5454</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3244,10 +3166,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444272</v>
+        <v>444350</v>
       </c>
       <c r="R24" t="n">
-        <v>6923791</v>
+        <v>6923880</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3279,7 +3201,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3289,7 +3211,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3320,45 +3242,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129926714</v>
+        <v>119385353</v>
       </c>
       <c r="B25" t="n">
-        <v>91901</v>
+        <v>91282</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1503</v>
+        <v>5685</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Högfjället, Hjd</t>
+          <t>Järpbäcken, Järpbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444331</v>
+        <v>444017</v>
       </c>
       <c r="R25" t="n">
-        <v>6923827</v>
+        <v>6923752</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3385,22 +3307,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3415,7 +3337,7 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -3423,18 +3345,14 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Mellanskog AB - Högfjället</t>
-        </is>
-      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129926731</v>
+        <v>129926737</v>
       </c>
       <c r="B26" t="n">
-        <v>78938</v>
+        <v>93235</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3442,37 +3360,46 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>5966</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444190</v>
+        <v>444073</v>
       </c>
       <c r="R26" t="n">
-        <v>6923908</v>
+        <v>6923833</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3501,7 +3428,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3511,7 +3438,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3542,45 +3469,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129926700</v>
+        <v>129926706</v>
       </c>
       <c r="B27" t="n">
-        <v>78938</v>
+        <v>90710</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444139</v>
+        <v>444279</v>
       </c>
       <c r="R27" t="n">
-        <v>6923624</v>
+        <v>6923782</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3612,7 +3548,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3622,7 +3558,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3653,10 +3589,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129926737</v>
+        <v>129926730</v>
       </c>
       <c r="B28" t="n">
-        <v>93048</v>
+        <v>78730</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3664,46 +3600,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5966</v>
+        <v>6437</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444073</v>
+        <v>444200</v>
       </c>
       <c r="R28" t="n">
-        <v>6923833</v>
+        <v>6923914</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3732,7 +3659,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3742,7 +3669,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3773,10 +3700,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129926726</v>
+        <v>129926736</v>
       </c>
       <c r="B29" t="n">
-        <v>57985</v>
+        <v>79084</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3784,21 +3711,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3808,13 +3735,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444309</v>
+        <v>444093</v>
       </c>
       <c r="R29" t="n">
-        <v>6923959</v>
+        <v>6923866</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3843,7 +3770,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3853,7 +3780,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3884,10 +3811,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129926696</v>
+        <v>129926725</v>
       </c>
       <c r="B30" t="n">
-        <v>80285</v>
+        <v>79946</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3895,21 +3822,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3919,10 +3846,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444018</v>
+        <v>444315</v>
       </c>
       <c r="R30" t="n">
-        <v>6923684</v>
+        <v>6923974</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3954,7 +3881,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3964,7 +3891,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3995,54 +3922,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129926729</v>
+        <v>129926696</v>
       </c>
       <c r="B31" t="n">
-        <v>93010</v>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444210</v>
+        <v>444018</v>
       </c>
       <c r="R31" t="n">
-        <v>6923955</v>
+        <v>6923684</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4074,7 +3992,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4084,7 +4002,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4115,57 +4033,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129926697</v>
+        <v>129926705</v>
       </c>
       <c r="B32" t="n">
-        <v>57826</v>
+        <v>80467</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444080</v>
+        <v>444117</v>
       </c>
       <c r="R32" t="n">
-        <v>6923635</v>
+        <v>6923735</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4194,7 +4103,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4204,7 +4113,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4238,7 +4147,7 @@
         <v>129926712</v>
       </c>
       <c r="B33" t="n">
-        <v>80320</v>
+        <v>80467</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4346,10 +4255,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129926705</v>
+        <v>129926738</v>
       </c>
       <c r="B34" t="n">
-        <v>80320</v>
+        <v>80467</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4381,13 +4290,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444117</v>
+        <v>444051</v>
       </c>
       <c r="R34" t="n">
-        <v>6923735</v>
+        <v>6923830</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4416,7 +4325,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4426,7 +4335,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4457,10 +4366,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129926718</v>
+        <v>129926704</v>
       </c>
       <c r="B35" t="n">
-        <v>97797</v>
+        <v>80468</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4468,21 +4377,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221941</v>
+        <v>6464</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4492,10 +4401,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444362</v>
+        <v>444124</v>
       </c>
       <c r="R35" t="n">
-        <v>6923872</v>
+        <v>6923727</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4527,7 +4436,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4537,7 +4446,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4568,10 +4477,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129926698</v>
+        <v>129926697</v>
       </c>
       <c r="B36" t="n">
-        <v>79770</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4579,34 +4488,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444118</v>
+        <v>444080</v>
       </c>
       <c r="R36" t="n">
-        <v>6923621</v>
+        <v>6923635</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4638,7 +4556,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4648,7 +4566,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4679,10 +4597,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129926715</v>
+        <v>129926726</v>
       </c>
       <c r="B37" t="n">
-        <v>92370</v>
+        <v>58114</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4690,21 +4608,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5454</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4714,10 +4632,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>444350</v>
+        <v>444309</v>
       </c>
       <c r="R37" t="n">
-        <v>6923880</v>
+        <v>6923959</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4749,7 +4667,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4759,7 +4677,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4790,45 +4708,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129926734</v>
+        <v>119385416</v>
       </c>
       <c r="B38" t="n">
-        <v>78846</v>
+        <v>99022</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>220093</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Högfjället, Hjd</t>
+          <t>Järpbäcken, Järpbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444169</v>
+        <v>444008</v>
       </c>
       <c r="R38" t="n">
-        <v>6923886</v>
+        <v>6923751</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4855,22 +4773,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4885,7 +4803,7 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -4893,53 +4811,58 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Mellanskog AB - Högfjället</t>
-        </is>
-      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129926704</v>
+        <v>119386444</v>
       </c>
       <c r="B39" t="n">
-        <v>80321</v>
+        <v>109815</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>220204</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Högfjället, Hjd</t>
+          <t>Järpbäcken, Järpbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444124</v>
+        <v>444191</v>
       </c>
       <c r="R39" t="n">
-        <v>6923727</v>
+        <v>6923760</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4966,22 +4889,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4996,7 +4919,7 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
@@ -5004,62 +4927,58 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Mellanskog AB - Högfjället</t>
-        </is>
-      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129926710</v>
+        <v>119386449</v>
       </c>
       <c r="B40" t="n">
-        <v>93010</v>
+        <v>109815</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>220204</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Högfjället, Hjd</t>
+          <t>Järpbäcken, Järpbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444283</v>
+        <v>444184</v>
       </c>
       <c r="R40" t="n">
-        <v>6923819</v>
+        <v>6923782</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5086,22 +5005,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5116,7 +5035,7 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -5124,18 +5043,14 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>Mellanskog AB - Högfjället</t>
-        </is>
-      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129926720</v>
+        <v>119384834</v>
       </c>
       <c r="B41" t="n">
-        <v>91901</v>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5143,34 +5058,43 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Högfjället, Hjd</t>
+          <t>Järpbäcken, Järpbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444360</v>
+        <v>443997</v>
       </c>
       <c r="R41" t="n">
-        <v>6923918</v>
+        <v>6923843</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5197,22 +5121,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5227,7 +5151,7 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
@@ -5235,53 +5159,58 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>Mellanskog AB - Högfjället</t>
-        </is>
-      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129926721</v>
+        <v>119385001</v>
       </c>
       <c r="B42" t="n">
-        <v>79770</v>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Högfjället, Hjd</t>
+          <t>Järpbäcken, Järpbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444365</v>
+        <v>443985</v>
       </c>
       <c r="R42" t="n">
-        <v>6923915</v>
+        <v>6923818</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5308,22 +5237,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5338,7 +5267,7 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -5346,18 +5275,14 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t>Mellanskog AB - Högfjället</t>
-        </is>
-      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129926706</v>
+        <v>119385327</v>
       </c>
       <c r="B43" t="n">
-        <v>90538</v>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5365,43 +5290,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6286</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Högfjället, Hjd</t>
+          <t>Järpbäcken, Järpbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444279</v>
+        <v>444017</v>
       </c>
       <c r="R43" t="n">
-        <v>6923782</v>
+        <v>6923752</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5428,22 +5344,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5458,7 +5374,7 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
@@ -5466,56 +5382,61 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>Mellanskog AB - Högfjället</t>
-        </is>
-      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129926724</v>
+        <v>119385865</v>
       </c>
       <c r="B44" t="n">
-        <v>78938</v>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Högfjället, Hjd</t>
+          <t>Järpbäcken, Järpbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444330</v>
+        <v>444049</v>
       </c>
       <c r="R44" t="n">
-        <v>6923984</v>
+        <v>6923640</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5539,22 +5460,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5569,7 +5490,7 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
@@ -5577,53 +5498,58 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Mellanskog AB - Högfjället</t>
-        </is>
-      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129926728</v>
+        <v>119386311</v>
       </c>
       <c r="B45" t="n">
-        <v>91781</v>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Högfjället, Hjd</t>
+          <t>Järpbäcken, Järpbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444229</v>
+        <v>444071</v>
       </c>
       <c r="R45" t="n">
-        <v>6923882</v>
+        <v>6923737</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5650,22 +5576,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5680,7 +5606,7 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
@@ -5688,56 +5614,52 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY45" t="inlineStr">
-        <is>
-          <t>Mellanskog AB - Högfjället</t>
-        </is>
-      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129926709</v>
+        <v>119386336</v>
       </c>
       <c r="B46" t="n">
-        <v>91651</v>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3242</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Högfjället, Hjd</t>
+          <t>Järpbäcken, Järpbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444268</v>
+        <v>444060</v>
       </c>
       <c r="R46" t="n">
-        <v>6923829</v>
+        <v>6923853</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5761,22 +5683,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5791,7 +5713,7 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
@@ -5799,53 +5721,58 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Mellanskog AB - Högfjället</t>
-        </is>
-      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129926701</v>
+        <v>119386491</v>
       </c>
       <c r="B47" t="n">
-        <v>105987</v>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Högfjället, Hjd</t>
+          <t>Järpbäcken, Järpbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444126</v>
+        <v>444066</v>
       </c>
       <c r="R47" t="n">
-        <v>6923694</v>
+        <v>6923830</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5872,22 +5799,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5902,7 +5829,7 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
@@ -5910,18 +5837,14 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Mellanskog AB - Högfjället</t>
-        </is>
-      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>129926702</v>
       </c>
       <c r="B48" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6038,48 +5961,57 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129926730</v>
+        <v>129926703</v>
       </c>
       <c r="B49" t="n">
-        <v>78583</v>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>444200</v>
+        <v>444124</v>
       </c>
       <c r="R49" t="n">
-        <v>6923914</v>
+        <v>6923712</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6108,7 +6040,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6118,7 +6050,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6149,32 +6081,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129926733</v>
+        <v>129926701</v>
       </c>
       <c r="B50" t="n">
-        <v>79770</v>
+        <v>106243</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>221144</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6184,13 +6116,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444163</v>
+        <v>444126</v>
       </c>
       <c r="R50" t="n">
-        <v>6923898</v>
+        <v>6923694</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6219,7 +6151,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6229,7 +6161,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6260,48 +6192,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129926736</v>
+        <v>119385107</v>
       </c>
       <c r="B51" t="n">
-        <v>78937</v>
+        <v>106229</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>221725</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Högfjället, Hjd</t>
+          <t>Järpbäcken, Järpbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444093</v>
+        <v>443985</v>
       </c>
       <c r="R51" t="n">
-        <v>6923866</v>
+        <v>6923818</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6325,22 +6257,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6355,7 +6287,7 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
@@ -6363,65 +6295,52 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>Mellanskog AB - Högfjället</t>
-        </is>
-      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129926703</v>
+        <v>129926718</v>
       </c>
       <c r="B52" t="n">
-        <v>98920</v>
+        <v>97989</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444124</v>
+        <v>444362</v>
       </c>
       <c r="R52" t="n">
-        <v>6923712</v>
+        <v>6923872</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6450,7 +6369,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6460,7 +6379,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6491,10 +6410,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129926713</v>
+        <v>129926700</v>
       </c>
       <c r="B53" t="n">
-        <v>91651</v>
+        <v>79085</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6502,21 +6421,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3242</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6526,10 +6445,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444347</v>
+        <v>444139</v>
       </c>
       <c r="R53" t="n">
-        <v>6923828</v>
+        <v>6923624</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6561,7 +6480,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6571,12 +6490,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Under grov, gammal nedfallen tallgren.</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6607,10 +6521,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129926717</v>
+        <v>129926707</v>
       </c>
       <c r="B54" t="n">
-        <v>91742</v>
+        <v>79085</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6618,21 +6532,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1204</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6642,10 +6556,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444352</v>
+        <v>444272</v>
       </c>
       <c r="R54" t="n">
-        <v>6923879</v>
+        <v>6923791</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6677,7 +6591,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6687,7 +6601,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6718,32 +6632,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129926735</v>
+        <v>129926724</v>
       </c>
       <c r="B55" t="n">
-        <v>91901</v>
+        <v>79085</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6753,10 +6667,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444143</v>
+        <v>444330</v>
       </c>
       <c r="R55" t="n">
-        <v>6923881</v>
+        <v>6923984</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -6788,7 +6702,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6798,7 +6712,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6829,32 +6743,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129926716</v>
+        <v>129926731</v>
       </c>
       <c r="B56" t="n">
-        <v>91901</v>
+        <v>79085</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6864,10 +6778,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444351</v>
+        <v>444190</v>
       </c>
       <c r="R56" t="n">
-        <v>6923878</v>
+        <v>6923908</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6899,7 +6813,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6909,7 +6823,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6940,10 +6854,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129926708</v>
+        <v>129926698</v>
       </c>
       <c r="B57" t="n">
-        <v>79770</v>
+        <v>79917</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6975,10 +6889,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>444257</v>
+        <v>444118</v>
       </c>
       <c r="R57" t="n">
-        <v>6923818</v>
+        <v>6923621</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7010,7 +6924,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7020,7 +6934,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7044,6 +6958,667 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129926699</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>444138</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6923625</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>129926708</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>444257</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6923818</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>129926721</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>444365</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6923915</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>129926727</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>444295</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6923949</v>
+      </c>
+      <c r="S61" t="n">
+        <v>4</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>129926733</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>444163</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6923898</v>
+      </c>
+      <c r="S62" t="n">
+        <v>3</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>129926719</v>
+      </c>
+      <c r="B63" t="n">
+        <v>93227</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6332402</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Phellodon resupinatus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>nom. prov.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>444365</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6923923</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
         <is>
           <t>Mellanskog AB - Högfjället</t>
         </is>

--- a/artfynd/A 58107-2025 artfynd.xlsx
+++ b/artfynd/A 58107-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AZ63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926723</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119385161</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119385475</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119385432</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1235,6 +1260,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926734</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1342,6 +1372,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119386001</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1453,6 +1488,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926717</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1560,6 +1600,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119386464</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1671,6 +1716,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926714</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1782,6 +1832,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926716</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1893,6 +1948,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926720</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2004,6 +2064,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926735</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2115,6 +2180,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926728</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2222,6 +2292,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119385016</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2329,6 +2404,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119386274</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2440,6 +2520,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926709</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2556,6 +2641,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926713</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2661,6 +2751,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119395143</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2777,6 +2872,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119386422</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2897,6 +2997,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926710</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3008,6 +3113,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926722</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3128,6 +3238,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926729</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3239,6 +3354,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926715</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3346,6 +3466,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119385353</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3466,6 +3591,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926737</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3586,6 +3716,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926706</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3697,6 +3832,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926730</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3808,6 +3948,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926736</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3919,6 +4064,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926725</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4030,6 +4180,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926696</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4141,6 +4296,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926705</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4252,6 +4412,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926712</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4363,6 +4528,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926738</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4474,6 +4644,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926704</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4594,6 +4769,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926697</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4705,6 +4885,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926726</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4812,6 +4997,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119385416</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4928,6 +5118,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119386444</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5044,6 +5239,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119386449</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5160,6 +5360,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119384834</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5276,6 +5481,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119385001</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5383,6 +5593,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119385327</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5499,6 +5714,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119385865</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5615,6 +5835,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119386311</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5722,6 +5947,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119386336</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5838,6 +6068,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119386491</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5958,6 +6193,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926702</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6078,6 +6318,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926703</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6189,6 +6434,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926701</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6296,6 +6546,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119385107</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6407,6 +6662,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926718</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6518,6 +6778,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926700</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6629,6 +6894,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926707</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6740,6 +7010,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926724</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6851,6 +7126,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926731</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6962,6 +7242,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926698</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7073,6 +7358,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926699</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7184,6 +7474,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926708</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7295,6 +7590,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926721</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7406,6 +7706,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926727</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7517,6 +7822,11 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926733</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7623,8 +7933,77 @@
           <t>Mellanskog AB - Högfjället</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926719</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>